--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -492,19 +492,16 @@
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>BSMV hariç.Güncellenme Tarihi: 01.03.2020 00:00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -560,19 +557,16 @@
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>BSMV Hariç. 0-8.300 TL arası 39,87 TL;8.300,01-399.000 TL arası 57,14 TL; 399.000 TL üzeri 797,68 TL masraflıdır.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -595,14 +589,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -625,14 +616,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -655,14 +643,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -685,14 +670,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -800,19 +782,16 @@
           <t>27.84TL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>27.84TL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -830,19 +809,16 @@
           <t>55.69TL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>55.69TL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -860,19 +836,16 @@
           <t>398.83TL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>398.83TL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -890,19 +863,16 @@
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>BSMV Hariç Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -920,19 +890,16 @@
           <t>79.76TL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>79.76TL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>BSMV Hariç Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -950,19 +917,16 @@
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>BSMV Hariç Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1100,19 +1064,16 @@
           <t>27.85TL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>27.85TL</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1130,19 +1091,16 @@
           <t>199.42TL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>199.42TL</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1160,19 +1118,16 @@
           <t>19.94TL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>19.94TL</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1190,19 +1145,16 @@
           <t>39.88TL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>39.88TL</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1220,19 +1172,16 @@
           <t>398.84TL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>398.84TL</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1270,7 +1219,6 @@
           <t>Garanti BBVA International'dan Gelen Havale. BSMV hariç.Güncellenme Tarihi: 05.02.2026 00:00</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1288,19 +1236,16 @@
           <t>15.00USD</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>220.00USD</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>BSMV Hariç.İnternetten yapılırsa asgari tutar 5 USD, azami tutar 80 USD. Güncellenme Tarihi: 01.03.2020 00:00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1318,19 +1263,16 @@
           <t>190.48TL</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>190.48TL</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>BSMV Hariç. İşlem bazında ve mesajın çekildiği anda. Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1348,19 +1290,16 @@
           <t>309.52TL</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>309.52TL</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>BSMV Hariç. Güncellenme Tarihi:10.12.2025 00:00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1398,7 +1337,6 @@
           <t>BSMV Hariç. Güncellenme Tarihi:10.12.2025 00:00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1416,19 +1354,16 @@
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>BSMV Hariç. Güncellenme Tarihi:10.12.2025 00:00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1466,7 +1401,6 @@
           <t>BSMV Hariç. Güncellenme Tarihi:10.12.2025 00:00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1504,7 +1438,6 @@
           <t>BSMV hariç.Güncellenme Tarihi: 05.02.2026 00:00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1522,19 +1455,16 @@
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 05.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1552,19 +1482,16 @@
           <t>1250.00TL</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>1250.00TL</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 05.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1582,19 +1509,16 @@
           <t>1500.00TL</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>1500.00TL</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 05.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1632,7 +1556,6 @@
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 05.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1650,19 +1573,16 @@
           <t>2485.72TL</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>2485.72TL</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1680,19 +1600,16 @@
           <t>2733.34TL</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>2733.34TL</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1710,19 +1627,16 @@
           <t>2923.81TL</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>2923.81TL</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1760,7 +1674,6 @@
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1778,19 +1691,16 @@
           <t>50.00TL</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>50.00TL</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 01.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1808,19 +1718,16 @@
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 01.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1838,19 +1745,16 @@
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>BSMV Hariç. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1868,19 +1772,16 @@
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>BSMV Hariç. Güncellenme Tarihi: 06.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1898,19 +1799,16 @@
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1928,19 +1826,16 @@
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1958,19 +1853,16 @@
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -1988,19 +1880,16 @@
           <t>28570.00TL</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2018,19 +1907,16 @@
           <t>23805.00TL</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2048,19 +1934,16 @@
           <t>20950.00TL</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2078,19 +1961,16 @@
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>Son 1 sene ücretsiz. 1 seneden eski- 3 seneden yeni tarihli dökümanlar 28.58 TL. 3 seneden eski tarihli dökümanlar 287.62 TL'dir.BSMV hariç.Güncellenme Tarihi: 05.02.2026 00:00</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2128,7 +2008,6 @@
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2146,19 +2025,16 @@
           <t>85.72TL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>85.72TL</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>BSMV hariç. Değerli kağıt vergisi hariç. Tutar şube kanalına aittir. Dijitalden çek başvurusunda ücret 76,20 TL'dir. Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2176,19 +2052,16 @@
           <t>133.34TL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>133.34TL</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2226,7 +2099,6 @@
           <t>BSMV Hariç.Güncellenme Tarihi: 01.04.2020 00:00</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2244,19 +2116,16 @@
           <t>114.29TL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>114.29TL</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2274,19 +2143,16 @@
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2304,19 +2170,16 @@
           <t>438.10TL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>438.10TL</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2334,19 +2197,16 @@
           <t>1469.52TL</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>1469.52TL</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 14.04.2026 00:00</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2384,7 +2244,6 @@
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2402,19 +2261,16 @@
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2432,7 +2288,6 @@
           <t>45.00USD</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>45.00USD</t>
@@ -2448,7 +2303,6 @@
           <t>BSMV Hariç. Muhabir borç geçtiğinde, muhabirin borç geçtiği tutar;İşlem bazında Ödeme anında (Yurtdışından Tahsile Gelen Çeklerin Ödenmesi (Normal YP Çek) Güncellenme Tarihi: 01.04.2021 00:00</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2466,19 +2320,16 @@
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2496,19 +2347,16 @@
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2556,19 +2404,16 @@
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2586,19 +2431,16 @@
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2616,19 +2458,16 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2646,19 +2485,16 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 09.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2676,19 +2512,16 @@
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>BSMV Dahil .Güncellenme Tarihi: 09.02.2026 17:35</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2706,19 +2539,16 @@
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>BSMV Dahil .Güncellenme Tarihi: 09.02.2026 17:35</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2736,19 +2566,16 @@
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 22.07.2026 00:00</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2766,19 +2593,16 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>232.23TL</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>BSMV Hariç. Azami Tutar Satıcı Komisyonudur. Alıcı komisyonu min. 3,99 TL max 99,71 TL'dir. Güncellenme Tarihi: 06.01.2026</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2826,8 +2650,6 @@
           <t>5.00TL</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>3.50%</t>
@@ -2838,7 +2660,6 @@
           <t>Bu ücretler tahsilat sistemi anlaşması bulunan site vb. kurumlar için de geçerlidir. 149.99 TL’ye kadar olan ödemelerde asgâri tutar, 150.00 TL ve üzeri ödemelerde azami oran tahsil edilir. BSMV dahil.Güncellenme Tarihi: 25.07.2023</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2856,19 +2677,16 @@
           <t>30.00TL</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>36.00TL</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>BSMV Hariç. Bilyoner, Nesine, Tuttur, Oley, Misli, Sisal Şans, Birebin, TJK için tahsilat yapılmaktadır. Kanal bazında ücret farklılık göstermektedir. Güncellenme Tarihi: 01.01.2026 00:00</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2916,19 +2734,16 @@
           <t>15975.00TL</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>81665.00TL</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2946,19 +2761,16 @@
           <t>17135.00TL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>227785.00TL</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV dahildir.</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -2976,15 +2788,11 @@
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3002,19 +2810,16 @@
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir.</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3032,8 +2837,6 @@
           <t>10000.00TL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>6.50%</t>
@@ -3044,7 +2847,6 @@
           <t>Yıllık max oranı geçmeyecek şekilde dönemsel olarak tahsil edilir. %6,5'in 10000 TL'den daha düşük olması halinde 10000 TL komisyon tahsil edilir. BSMV Hariç.</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3062,8 +2864,6 @@
           <t>10000.00TL</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>6.50%</t>
@@ -3074,7 +2874,6 @@
           <t>Yıllık max oranı geçmeyecek şekilde dönemsel olarak tahsil edilir. %6,5'in 10000 TL'den daha düşük olması halinde 10000 TL komisyon tahsil edilir. BSMV Hariç.</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3182,8 +2981,6 @@
           <t>45USD</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>0.15%</t>
@@ -3194,7 +2991,6 @@
           <t>İşlem bazında - Ödeme anında (Yurtdışından Tahsile Gelen Çeklerin Ödenmesi (normal YP Çek)</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3212,7 +3008,6 @@
           <t>40USD</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>240USD</t>
@@ -3228,7 +3023,6 @@
           <t>İşlem Bazında ve transfer aşamasında (İleri gün valörlü peşin ve mal mukabili ithalat ödemeleri)</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3246,19 +3040,16 @@
           <t>4000.00TL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>4000.00TL</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>BSMV Hariç.Güncellenme Tarihi: 07.08.2025 00:00</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3276,8 +3067,6 @@
           <t>2600.00TL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -3288,7 +3077,6 @@
           <t>BSMV hariç.</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3306,15 +3094,11 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir.</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3332,15 +3116,11 @@
           <t>1350</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir.</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3358,19 +3138,16 @@
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>BSMV eklenir.</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3393,14 +3170,11 @@
           <t>1.15%</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>BSMV eklenir.</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3448,19 +3222,16 @@
           <t>99.00TL</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>2400.00TL</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>Asıl ve ek kartlarınızı, kayıp/çalıntı vb. nedenler ile 1 takvim yılı içinde 2 kez ücretsiz yenileyebilirsiniz. 3. yenilemeden itibaren ise her bir kart yenilemesinde;American Express Metal The Platinum Card için 2.400 TL, Bonus Platinum Biyometrik kart için 500 TL, diğer kartlar için 99 TL ücret yansıtılacaktır.</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3498,7 +3269,6 @@
           <t>0 -1,500 TL'ye %2.00+15 TL - 1,500 -5,000 TL'ye %2.00+30 TL - 5,000 TL üzerine %1.50+40 TL ücret alınır ve BSMV eklenir.</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3717,14 +3487,11 @@
           <t>1.00%</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>Karttan Havale/EFT işlemlerinde işlem tutarı üzerinden %1 oranında nakit avans işlem ücreti uygulanır (BSMV Hariç). Buna ek olarak,Garanti BBVA Mobil ve İnternet Bankacılığı’ndan yapılan işlemlerde:EFT işlemleri için 0-8.300 TL arasına 7,97 TL, 8.300-399.000 TL arasına 15,96 TL, 399.000 TL üzerine ise 199,41 TL EFT ücreti, Havale işlemleri için 0-8.300 TL arasına 3,99 TL, 8.300-399.000 TL arasına 7,98 TL, 399.000 TL üzerine ise 99,71 TL havale ücreti alınacaktır (BSMV hariç).Garanti BBVA ATM’lerinden yapılan işlemlerde:EFT işlemleri için 0-8.300 TL arasına 27,84 TL, 8.300-399.000 TL arasına 55,69 TL, 399.000 TL üzerine ise 398,83 TL EFT ücreti, Havale işlemleri için 0-8.300 TL arasına 13,92 TL, 8.300-399.000 TL arasına 27,85 TL, 399.000 TL üzerine ise 199,42 TL havale ücreti alınacaktır (BSMV hariç).Ayrıca Karttan Havale/EFT kullanımlarında işlem tarihinden itibaren günlük nakit faizi işletilir.</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3742,19 +3509,16 @@
           <t>140.00TL</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>3000.00TL</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>Asıl ve ek kartlarınızı, kayıp/çalıntı vb. nedenler ile 1 takvim yılı içinde 2 kez ücretsiz yenileyebilirsiniz. 3. yenilemeden itibaren ise her bir kart yenilemesinde; American Express Metal The Platinum için 3.000 TL, Bonus Platinum Biyometrik için 1.547 TL, Bonus Platinum Dinamik için 1.066 TL, diger kartlar için 140 TL ücret yansıtılacaktır.</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3777,14 +3541,11 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>100 TL altı işlemler için Asgari Tutar , 100 TL ve üzerindeki işlemler için Asgari Oran uygulanır.</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3802,15 +3563,11 @@
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3828,19 +3585,16 @@
           <t>750.00TL</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>750.00TL</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>BSMV dahildir. 6 aylık dönemlerde, yılda iki kere tahsilat yapılmaktadır.Yabancı para cinsi vadesiz hesaplardan yapılacak tahsilatlarda 750 TL muadili ücret tahsilat anında; açıklanan en güncel merkez bankası döviz kuruna göre belirlenecektir</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3888,19 +3642,16 @@
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>Muadili ücret tahsil edilmektedir. Talep edilen ekstre başına tahsilat yapılmaktadır. BSMV dahildir.</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3918,19 +3669,16 @@
           <t>250.00TL</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>250.00TL</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>Hisse senedi hesaplarından 6 ayda bir 250 TL (BSMV dahil) (yıllık 500 TL (BSMV dahil)) hesap bakım ücreti tahsil edilmektedir. Yıllık hesap bakım ücreti hisse senedi satış takas tutarı içerisinden tahsil edilir. İlgili tutarlarda değişiklik olması durumunda internet sayfamızda güncellenmektedir.</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3953,7 +3701,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -3964,7 +3711,6 @@
           <t>Hesap açılışında komisyon oranı sabit 0,084% (onbinde 8,4) olarak atanmaktadır. Oranlar işlem başına olup, BSMV dahil değildir. Sözleşmelerde belirtildiği üzere yapılan her işlemde (alım/satım), kurum azami BSMV hariç binde 1,05 oranında komisyon tahsilatı yapma hakkına sahiptir. BSMV oranı işlemden kesilen komisyonun yüzde 5’idir.</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3987,7 +3733,6 @@
           <t>0.001%</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>0.001%</t>
@@ -3998,7 +3743,6 @@
           <t>BSMV hariç.</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4021,14 +3765,11 @@
           <t>0.01%</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>İşlem Piyasa Değeri</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4046,15 +3787,11 @@
           <t>139.21TL</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>İşlem sayısı</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4072,15 +3809,11 @@
           <t>1.39TL</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>İşlem sayısı</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4098,15 +3831,11 @@
           <t>17.75TL</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>Açılan hesap başına</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4124,7 +3853,6 @@
           <t>13.05TL</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>25.78TL</t>
@@ -4140,7 +3868,6 @@
           <t>Talimat sayısı</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4158,7 +3885,6 @@
           <t>1.38TL</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>6.90TL</t>
@@ -4174,7 +3900,6 @@
           <t>Talimat sayısı</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4192,19 +3917,16 @@
           <t>160.00TL</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>180.00TL</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4252,19 +3974,16 @@
           <t>0TL</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>300.00TL</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4282,19 +4001,16 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>945.00TL</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4312,19 +4028,16 @@
           <t>980.00TL</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>1665.00TL</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4342,19 +4055,16 @@
           <t>1300.00TL</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>1980.00TL</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4372,19 +4082,16 @@
           <t>540.00TL</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir.</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>31.07.2026</t>

--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -589,11 +589,14 @@
           <t>2.9%</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
-        </is>
-      </c>
+          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -616,11 +619,14 @@
           <t>2.9%</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
-        </is>
-      </c>
+          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -643,11 +649,14 @@
           <t>2.9%</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
-        </is>
-      </c>
+          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -670,11 +679,14 @@
           <t>2.9%</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
-        </is>
-      </c>
+          <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3701,6 +3713,7 @@
           <t>0.084%</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -3708,9 +3721,10 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hesap açılışında komisyon oranı sabit 0,084% (onbinde 8,4) olarak atanmaktadır. Oranlar işlem başına olup, BSMV dahil değildir. Sözleşmelerde belirtildiği üzere yapılan her işlemde (alım/satım), kurum azami BSMV hariç binde 1,05 oranında komisyon tahsilatı yapma hakkına sahiptir. BSMV oranı işlemden kesilen komisyonun yüzde 5’idir.</t>
-        </is>
-      </c>
+          <t>Hesap açılışında komisyon oranı sabit 0,084% (onbinde 8,4) olarak atanmaktadır. Oranlar işlem başına olup, BSMV dahil değildir. Sözleşmelerde belirtildiği üzere yapılan her işlemde (alım/satım), kurum azami BSMV hariç binde 1,05 oranında komisyon tahsilatı yapma hakkına sahiptir. BSMV oranı işlemden kesilen komisyonun yüzde 5’idir.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4093,6 +4107,32 @@
         </is>
       </c>
       <c r="H128" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>İntifa</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.39TL</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>İşlem sayısı</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
         <is>
           <t>31.07.2026</t>
         </is>

--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -589,14 +589,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -619,14 +616,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -649,14 +643,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -679,14 +670,11 @@
           <t>2.9%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>BSMV Hariç. Oran limit üzeri çekilen tutara aittir. İşleme ilişkin ücret tutarı ve oran değişebilecektir. ATM’lerden yapılacak işlem anında müşteri bilgilendirmesi yapılarak onay alınır. Güncellenme Tarihi: 10.07.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -3713,7 +3701,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -3724,7 +3711,6 @@
           <t>Hesap açılışında komisyon oranı sabit 0,084% (onbinde 8,4) olarak atanmaktadır. Oranlar işlem başına olup, BSMV dahil değildir. Sözleşmelerde belirtildiği üzere yapılan her işlemde (alım/satım), kurum azami BSMV hariç binde 1,05 oranında komisyon tahsilatı yapma hakkına sahiptir. BSMV oranı işlemden kesilen komisyonun yüzde 5’idir.</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -4123,15 +4109,11 @@
           <t>1.39TL</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>İşlem sayısı</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>31.07.2026</t>

--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -4073,13 +4073,11 @@
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>BSMV hariç</t>
@@ -4191,13 +4189,11 @@
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>BSMV Hariç. 0-8.300 TL arası 39,87 TL;8.300,01-399.000 TL arası 57,14 TL; 399.000 TL üzeri 797,68 TL masraflıdır</t>
@@ -4259,13 +4255,11 @@
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4293,13 +4287,11 @@
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4327,13 +4319,11 @@
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4361,13 +4351,11 @@
           <t>27.84TL</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>27.84TL</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4395,13 +4383,11 @@
           <t>55.69TL</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>55.69TL</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4429,13 +4415,11 @@
           <t>398.83TL</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>398.83TL</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4463,13 +4447,11 @@
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4497,13 +4479,11 @@
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4531,13 +4511,11 @@
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan EFT işlemlerinde EFT ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4565,13 +4543,11 @@
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -4599,13 +4575,11 @@
           <t>79.76TL</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>79.76TL</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -4633,13 +4607,11 @@
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -4667,13 +4639,11 @@
           <t>13.92TL</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>199.42TL</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -4701,13 +4671,11 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -4735,13 +4703,11 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4769,13 +4735,11 @@
           <t>7.98TL</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>7.98TL</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4803,13 +4767,11 @@
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4837,13 +4799,11 @@
           <t>13.92TL</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>13.92TL</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4871,13 +4831,11 @@
           <t>27.85TL</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>27.85TL</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4905,13 +4863,11 @@
           <t>199.42TL</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>199.42TL</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>BSMV Hariç. Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4939,13 +4895,11 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>BSMV Hariç.Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -4973,13 +4927,11 @@
           <t>7.98TL</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>7.98TL</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>BSMV Hariç.Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -5007,13 +4959,11 @@
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>BSMV Hariç.Kredi Kartından yapılan İşlemlerde EFT/Havale ücretine ek olarak %1 nakit avans ücreti ve nakit avans faizi uygulanmaktadır</t>
@@ -5041,13 +4991,11 @@
           <t>19.94TL</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>19.94TL</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5075,13 +5023,11 @@
           <t>39.88TL</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>39.88TL</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5109,13 +5055,11 @@
           <t>398.84TL</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>398.84TL</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5185,13 +5129,11 @@
           <t>15.00USD</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>220.00USD</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>BSMV Hariç.İnternetten yapılırsa asgari tutar 5 USD, azami tutar 80 USD</t>
@@ -5219,13 +5161,11 @@
           <t>190.48TL</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>190.48TL</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>BSMV Hariç. İşlem bazında ve mesajın çekildiği anda</t>
@@ -5253,13 +5193,11 @@
           <t>309.52TL</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>309.52TL</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5329,13 +5267,11 @@
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5400,10 +5336,6 @@
           <t>Moneysend (Gönderici)</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>işleme konu tutar için 750 TL'ye kadar %2+50 TL+BSMV, 751-2.000 TL arasında %2+85 TL+BSMV ve 2.001 TL üzerinde %2+150 TL+BSMV ücret alınır. Maksimum gönderim tutarı 5.000 USD ve muadilidir</t>
@@ -5426,13 +5358,11 @@
           <t>Moneysend (Alıcı)</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>4.50%</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -5507,13 +5437,11 @@
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5541,13 +5469,11 @@
           <t>1250.00TL</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>1250.00TL</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5575,13 +5501,11 @@
           <t>1500.00TL</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>1500.00TL</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>BSMV dahil.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5651,13 +5575,11 @@
           <t>2485.72TL</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>2485.72TL</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5685,13 +5607,11 @@
           <t>2733.34TL</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>2733.34TL</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5719,13 +5639,11 @@
           <t>2923.81TL</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>2923.81TL</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>BSMV hariç.Belirtilen ücretler para transferi komisyon ücreti olup, gönderim seçeneklerine bağlı olarak işleme aracılık eden bankalar tarafından muhabir bankası masrafı ayrıca tahsil edilebilecektir. Dolayısıyla Swift işlemlerinde alıcının eline geçen tutar gönderilen tutardan daha düşük olabilir</t>
@@ -5795,13 +5713,11 @@
           <t>50.00TL</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>50.00TL</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5829,13 +5745,11 @@
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5863,13 +5777,11 @@
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5897,13 +5809,11 @@
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -5931,13 +5841,11 @@
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -5965,13 +5873,11 @@
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -5999,13 +5905,11 @@
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6033,13 +5937,11 @@
           <t>28570.00TL</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6067,13 +5969,11 @@
           <t>23805.00TL</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6101,13 +6001,11 @@
           <t>20950.00TL</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>BSMV hariçtir.* Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6135,13 +6033,11 @@
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6169,13 +6065,11 @@
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6203,13 +6097,11 @@
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>BSMV dahildir. Söz konusu ücretler 18.05.2026 tarihi itibarıyla yeni açılan kiralık kasalar için geçerli fiyatlardır. Bu tarihten önce açılan kiralık kasalar ücretler bakımından farklılık gösterebilecektir. Söz konusu ücretlerde değişiklik yapılması halinde gerekli bilgilendirme yapılacaktır</t>
@@ -6237,13 +6129,11 @@
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>Son 1 sene ücretsiz. 1 seneden eski- 3 seneden yeni tarihli dökümanlar 28.58 TL. 3 seneden eski tarihli dökümanlar 287.62 TL'dir.BSMV hariç</t>
@@ -6266,14 +6156,11 @@
           <t>Konsolosluk İçin Mektup Düzenleme Ücreti</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>75.00TL</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -6343,13 +6230,11 @@
           <t>85.72TL</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>85.72TL</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>BSMV hariç. Değerli kağıt vergisi hariç. Tutar şube kanalına aittir. Dijitalden çek başvurusunda ücret 76,20 TL'dir</t>
@@ -6377,13 +6262,11 @@
           <t>133.34TL</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>133.34TL</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6453,13 +6336,11 @@
           <t>114.29TL</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>114.29TL</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6487,13 +6368,11 @@
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6521,13 +6400,11 @@
           <t>438.10TL</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>438.10TL</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6555,13 +6432,11 @@
           <t>1469.52TL</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>1469.52TL</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6631,13 +6506,11 @@
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6665,13 +6538,11 @@
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>323.81TL</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6699,7 +6570,6 @@
           <t>45.00USD</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>45.00USD</t>
@@ -6737,13 +6607,11 @@
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6771,13 +6639,11 @@
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6847,13 +6713,11 @@
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6881,13 +6745,11 @@
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6915,13 +6777,11 @@
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6949,13 +6809,11 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -6983,13 +6841,11 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -7017,13 +6873,11 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -7051,13 +6905,11 @@
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -7085,13 +6937,11 @@
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -7119,13 +6969,11 @@
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -7153,13 +7001,11 @@
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -7182,10 +7028,6 @@
           <t>PTT'den Para Gönderimi</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>PTT para gönderme işlemlerinde kendi tarifesini uygulamaktadır</t>
@@ -7208,13 +7050,11 @@
           <t>Havalimanı, Gümrük ve Sınır Bölgelerindeki Döviz / Efektif Alım Satımı</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>4.00%</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>4.00%</t>
@@ -7247,13 +7087,11 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>232.23TL</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
           <t>BSMV Hariç. Azami Tutar Satıcı Komisyonudur. Alıcı komisyonu min. 3,99 TL max 99,71 TL'dir</t>
@@ -7281,7 +7119,6 @@
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>134.00TL</t>
@@ -7319,8 +7156,6 @@
           <t>5.00TL</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>3.50%</t>
@@ -7353,13 +7188,11 @@
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>50.00TL</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>Bu ücretler tahsilat sistemi anlaşması bulunan site, vakıf vb. kurumlar için de geçerlidir. Fatura/aidat tahsilatı işlem ücretleri kurum ile banka arasında yapılan anlaşma bazında farklılaşmaktadır. Otomatik ödeme talimatıyla yapılan tahsilat işlemlerinden ücret alınmamaktadır. BSMV dahil</t>
@@ -7387,13 +7220,11 @@
           <t>30.00TL</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>36.00TL</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>BSMV Hariç. Bilyoner, Nesine, Tuttur, Oley, Misli, Sisal Şans, Birebin, TJK için tahsilat yapılmaktadır. Kanal bazında ücret farklılık göstermektedir</t>
@@ -7416,15 +7247,11 @@
           <t>36 ay vadeli 10.000 TL e-Kredi</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>4.10%</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -7442,15 +7269,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>7.94%</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -7468,15 +7291,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>4.10%</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -7494,15 +7313,11 @@
           <t>9 ay vadeli 3.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>4.75%</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -7520,9 +7335,6 @@
           <t>Avans Hesap</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -7550,14 +7362,11 @@
           <t>36 ay vadeli 10.000 TL e-Kredi</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>200.00TL</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>Sigorta primi; kredi tutarı, vadesi ve müşteri özelinde değişiklik gösterebilir</t>
@@ -7580,14 +7389,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>200.00TL</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Sigorta primi; kredi tutarı, vadesi ve müşteri özelinde değişiklik gösterebilir</t>
@@ -7610,14 +7416,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>200.00TL</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>Sigorta primi; kredi tutarı, vadesi ve müşteri özelinde değişiklik gösterebilir</t>
@@ -7640,14 +7443,11 @@
           <t>9 ay vadeli 3.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>45.00TL</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>Sigorta primi; kredi tutarı, vadesi ve müşteri özelinde değişiklik gösterebilir</t>
@@ -7670,14 +7470,11 @@
           <t>36 ay vadeli 10.000 TL e-Kredi</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>257.50TL</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Kredi tahsis ücreti, sigorta ve vergi dahil ücretler toplamından oluşmaktadır</t>
@@ -7700,14 +7497,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>257.50TL</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>Kredi tahsis ücreti, sigorta ve vergi dahil ücretler toplamından oluşmaktadır</t>
@@ -7730,14 +7524,11 @@
           <t>36 ay vadeli 10.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>257.50TL</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>Kredi tahsis ücreti, sigorta ve vergi dahil ücretler toplamından oluşmaktadır</t>
@@ -7760,14 +7551,11 @@
           <t>9 ay vadeli 3.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>62.25TL</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>Kredi tahsis ücreti, sigorta ve vergi dahil ücretler toplamından oluşmaktadır</t>
@@ -7790,9 +7578,6 @@
           <t>36 ay vadeli 10.000 TL e-Kredi</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -7820,9 +7605,6 @@
           <t>36 ay vadeli 10.000 TL Tutarlı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -7850,9 +7632,6 @@
           <t>36 ay vadeli 10.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -7880,9 +7659,6 @@
           <t>9 ay vadeli 3.000 TL Tutarlı Kampanyalı İhtiyaç Kredisi</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8014,9 +7790,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8044,9 +7817,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8074,9 +7844,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8104,9 +7871,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8134,9 +7898,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8164,9 +7925,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8194,9 +7952,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>3.60%</t>
@@ -8224,9 +7979,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi ( Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>3.60%</t>
@@ -8254,9 +8006,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için )</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>3.60%</t>
@@ -8284,9 +8033,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>3.50%</t>
@@ -8314,9 +8060,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>3.50%</t>
@@ -8344,9 +8087,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>3.50%</t>
@@ -8374,9 +8114,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>109.49%</t>
@@ -8404,9 +8141,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için )</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>109.49%</t>
@@ -8434,9 +8168,6 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>109.49%</t>
@@ -8464,9 +8195,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>108.65%</t>
@@ -8494,9 +8222,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>108.65%</t>
@@ -8524,9 +8249,6 @@
           <t>36 ay vadeli 30.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>108.65%</t>
@@ -8554,14 +8276,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 0 KM Taşıt Kredisi</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8584,14 +8303,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi ( Bankamızdan kaskosu olmayan 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8614,14 +8330,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için)</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8644,14 +8357,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 0 KM Taşıt Kredisi Rehin Kaldırma Ücreti</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8674,14 +8384,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi ( Bankamızdan kaskosu olmayan 2. el araçlar için) Rehin Kaldırma Ücreti</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8704,14 +8411,11 @@
           <t>24 ay vadeli 20.000 TL tutarlı 2. el Taşıt Kredisi (Bankamızdan kaskolu 2. el araçlar için) Rehin Kaldırma Ücreti</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -8734,9 +8438,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8764,9 +8465,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -8794,9 +8492,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8824,9 +8519,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -8854,9 +8546,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -8884,9 +8573,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -8914,9 +8600,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -8944,9 +8627,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -8974,14 +8654,11 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV hariçtir, kredi kullandığı tarih itibariyle üzerine kayıtlı konutu bulunan müşteriler için BSMV yansıtılır</t>
@@ -9004,14 +8681,11 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9034,14 +8708,11 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9064,14 +8735,11 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9094,14 +8762,11 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9124,14 +8789,11 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV hariçtir, kredi kullandığı tarih itibariyle üzerine kayıtlı konutu bulunan müşteriler için BSMV yansıtılır</t>
@@ -9154,14 +8816,11 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9184,14 +8843,11 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV dahildir</t>
@@ -9214,14 +8870,11 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
           <t>Tesis edilen ipotek başına tahsil edilen masraf tutarıdır. BSMV hariçtir, kredi kullandığı tarih itibariyle üzerine kayıtlı konutu bulunan müşteriler için BSMV yansıtılır</t>
@@ -9244,9 +8897,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>4.59%</t>
@@ -9274,9 +8924,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>4.30%</t>
@@ -9304,9 +8951,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>6.36%</t>
@@ -9334,9 +8978,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>6.36%</t>
@@ -9364,9 +9005,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>4.10%</t>
@@ -9394,9 +9032,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>5.45%</t>
@@ -9424,9 +9059,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>4.30%</t>
@@ -9454,9 +9086,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>5.45%</t>
@@ -9484,9 +9113,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>46.2876%</t>
@@ -9514,9 +9140,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>90.3622%</t>
@@ -9544,9 +9167,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>69.3835%</t>
@@ -9574,9 +9194,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>81.8393%</t>
@@ -9604,9 +9221,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>172.0543%</t>
@@ -9634,9 +9248,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>172.0543%</t>
@@ -9664,9 +9275,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>87.4587%</t>
@@ -9694,9 +9302,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>88.9740%</t>
@@ -9724,9 +9329,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>70.2241%</t>
@@ -9754,9 +9356,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>88.7544%</t>
@@ -9789,13 +9388,11 @@
           <t>31950.00TL</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>163330.00TL</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
           <t>(İki ekspertiz işlemi için) Ekspertiz ücreti değerlemeye konu gayrimenkullerin konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmetleri için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -9823,13 +9420,11 @@
           <t>15975.00TL</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>81665.00TL</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -9857,13 +9452,11 @@
           <t>15975.00TL</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>81665.00TL</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -9891,13 +9484,11 @@
           <t>15975.00TL</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>81665.00TL</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -9955,13 +9546,11 @@
           <t>15975.00TL</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>81665.00TL</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
           <t>Ekspertiz ücreti değerlemeye konu gayrimenkulün konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -10019,13 +9608,11 @@
           <t>31950.00TL</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>163330.00TL</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
           <t>(İki ekspertiz işlemi için) Ekspertiz ücreti değerlemeye konu gayrimenkullerin konumu, vasfı ve brüt alanına (m2) göre değişiklik göstermektedir. Ekspertiz hizmeti için yapılan işlem başına oluşan ve üçüncü kişilere, kurum/kuruluşlara ödenen maliyet tutarı tahsil edilir. BSMV’den muaftır</t>
@@ -10138,9 +9725,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -10168,9 +9752,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>3.08%</t>
@@ -10198,9 +9779,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>3.68%</t>
@@ -10228,9 +9806,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -10258,9 +9833,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -10340,10 +9912,6 @@
           <t>% 100 Mortgage</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10366,10 +9934,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10392,10 +9956,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10418,10 +9978,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10444,10 +10000,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10470,10 +10022,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10496,10 +10044,6 @@
           <t>Evini Değiştirene Mortgage</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10522,10 +10066,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10548,10 +10088,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10574,10 +10110,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>Kredi kullandırılan konutun bulunduğu yere ve inşa özelliklerine göre değişiklik göstermektedir</t>
@@ -10600,10 +10132,6 @@
           <t>% 100 Mortgage</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10626,10 +10154,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10652,10 +10176,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10678,10 +10198,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10704,10 +10220,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10730,10 +10242,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10756,10 +10264,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10782,10 +10286,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10808,10 +10308,6 @@
           <t>Evini Değiştirene Mortgage</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10834,10 +10330,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10860,10 +10352,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10886,10 +10374,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10912,10 +10396,6 @@
           <t>% 100 Mortgage</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10938,10 +10418,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10964,10 +10440,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -10990,10 +10462,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11016,10 +10484,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11042,10 +10506,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11068,10 +10528,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11094,10 +10550,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11120,10 +10572,6 @@
           <t>Evini Değiştirene Mortgage</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11146,10 +10594,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11172,10 +10616,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11198,10 +10638,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>Krediyi kullanan müşteri özelinde değişiklik göstermekte olup, zorunlu değildir</t>
@@ -11224,9 +10660,6 @@
           <t>% 100 Mortgage</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11254,9 +10687,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11284,9 +10714,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11314,9 +10741,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11344,9 +10768,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11374,9 +10795,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11404,9 +10822,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11434,9 +10849,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11464,9 +10876,6 @@
           <t>Evini Değiştirene Mortgage</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11494,9 +10903,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11524,9 +10930,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11554,9 +10957,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11584,9 +10984,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11614,9 +11011,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11644,9 +11038,6 @@
           <t>% 100 Mortgage</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11674,9 +11065,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Değişken Faizli Mortgage</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11704,9 +11092,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Kiracıya Mortgage</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11734,9 +11119,6 @@
           <t>120 ay vadeli 100.000 TL tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11764,9 +11146,6 @@
           <t>36 ay vadeli 50.000 TL Tutarlı Evini Gösterene Otomatik Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11794,9 +11173,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11824,9 +11200,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı Sabit Faizli Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11854,9 +11227,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11884,9 +11254,6 @@
           <t>Evini Değiştirene Mortgage</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -11914,9 +11281,6 @@
           <t>36 ay vadeli 125.000 TL Tutarlı Değişken Faizli Evini Gösterene Mortgage</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11944,9 +11308,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Evini Gösterene Hazır Mortgage</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -11974,9 +11335,6 @@
           <t>36 ay vadeli 125.000 TL tutarlı Sabit Faizli Evini Gösterene Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -12004,9 +11362,6 @@
           <t>60 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -12034,9 +11389,6 @@
           <t>96 ay vadeli 100.000 TL Tutarlı İşyeri Mortgage (GENEL)</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
           <t>0.58%</t>
@@ -12064,15 +11416,11 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>4.20%</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12095,9 +11443,6 @@
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir</t>
@@ -12120,15 +11465,11 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12146,15 +11487,11 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
           <t>4.10%</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12172,11 +11509,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12199,13 +11531,11 @@
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir</t>
@@ -12228,9 +11558,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -12258,14 +11585,11 @@
           <t>Rehin Ücreti</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -12288,9 +11612,6 @@
           <t>Tahsis Ücreti</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -12318,8 +11639,6 @@
           <t>Toplam Masraf Tutarı</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12330,7 +11649,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12348,8 +11666,6 @@
           <t>Vergi</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12360,7 +11676,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12378,9 +11693,6 @@
           <t>Yıllık Toplam Maliyet Oranı</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
           <t>23.2461%</t>
@@ -12408,9 +11720,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
           <t>8.00%</t>
@@ -12438,9 +11747,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
           <t>8.00%</t>
@@ -12468,14 +11774,11 @@
           <t>Rehin Ücreti</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -12498,9 +11801,6 @@
           <t>Tahsis Ücreti</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -12528,8 +11828,6 @@
           <t>Toplam Masraf Tutarı</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12540,7 +11838,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12558,8 +11855,6 @@
           <t>Vergi</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12570,7 +11865,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12588,9 +11882,6 @@
           <t>Yıllık Toplam Maliyet Oranı</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
           <t>23.6448%</t>
@@ -12618,9 +11909,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr"/>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
           <t>8.00%</t>
@@ -12648,14 +11936,11 @@
           <t>Rehin Ücreti</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>350.92TL</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -12678,9 +11963,6 @@
           <t>Tahsis Ücreti</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr"/>
-      <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
           <t>0.50%</t>
@@ -12708,8 +11990,6 @@
           <t>Toplam Masraf Tutarı</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12720,7 +12000,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12738,8 +12017,6 @@
           <t>Vergi</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -12750,7 +12027,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12768,9 +12044,6 @@
           <t>Yıllık Toplam Maliyet Oranı</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
-      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
           <t>23.3604%</t>
@@ -12798,9 +12071,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
           <t>16.99%</t>
@@ -12828,9 +12098,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -12858,9 +12125,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
           <t>16.99%</t>
@@ -12888,9 +12152,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -12918,15 +12179,11 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
           <t>96.00%</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -12944,10 +12201,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr"/>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>Kullandırılan kredinin %1 oranında tahsil edilir</t>
@@ -12970,14 +12223,11 @@
           <t>Teminat Tesis Ücreti</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>22.75TL</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>BSMV hariçtir</t>
@@ -13000,9 +12250,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr"/>
-      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
           <t>5.83%</t>
@@ -13030,9 +12277,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
           <t>1.155%</t>
@@ -13060,10 +12304,6 @@
           <t>Belge ve Bilgilendirme Ücreti (Ekstre Ücreti)</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>Ekstre gönderim maliyeti kadar ücret tahsil edilmektedir. Gönderim maliyeti değişkenlik göstermektedir</t>
@@ -13086,9 +12326,6 @@
           <t>Kredi Faizi</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
           <t>75.00%</t>
@@ -13116,9 +12353,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
           <t>1.10%</t>
@@ -13146,9 +12380,6 @@
           <t>Kredi Faizi</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
           <t>75.00%</t>
@@ -13176,9 +12407,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
           <t>1.10%</t>
@@ -13206,9 +12434,6 @@
           <t>Kredi Faizi</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr"/>
-      <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
           <t>75.00%</t>
@@ -13236,9 +12461,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
           <t>1.10%</t>
@@ -13266,10 +12488,6 @@
           <t>Belge ve Bilgilendirme Ücreti (Ekstre Ücreti)</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr"/>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>Ekstre gönderim maliyeti kadar ücret tahsil edilmektedir. Gönderim maliyeti değişkenlik göstermektedir</t>
@@ -13292,9 +12510,6 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
-      <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -13322,9 +12537,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
-      <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -13357,8 +12569,6 @@
           <t>10000.00TL</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
-      <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
           <t>6.50%</t>
@@ -13391,8 +12601,6 @@
           <t>10000.00TL</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
-      <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
           <t>6.50%</t>
@@ -13420,10 +12628,6 @@
           <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti (Ekspertiz Ücreti)</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>"Hizmetin 3. kişiden alınması durumunda 3. kişilere ödenen tutarın yüzde on beş fazlası,Hizmetin banka bünyesinde karşılanması halinde makul ücret"</t>
@@ -13446,10 +12650,6 @@
           <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti (İpotek Fek Ücreti – İşyeri Kredileri)</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>"Hizmetin 3. kişiden alınması durumunda 3. kişilere ödenen ücret,Hizmetin banka bünyesinde karşılanması halinde makul ücret"</t>
@@ -13472,10 +12672,6 @@
           <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti (Rehin Çözme Ücreti)</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>"Hizmetin 3. kişiden alınması durumunda 3. kişilere ödenen ücret,Hizmetin banka bünyesinde karşılanması halinde makul ücret"</t>
@@ -13498,10 +12694,6 @@
           <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti (Taşınmaz Rehin Ücreti - İşyeri Kredileri)</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
           <t>"Hizmetin 3. kişiden alınması durumunda 3. kişilere ödenen ücret,Hizmetin banka bünyesinde karşılanması halinde makul ücret"</t>
@@ -13524,10 +12716,6 @@
           <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti (Ticari Nitelikli İpotek Tesis Ücreti)</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>"Hizmetin 3. kişiden alınması durumunda 3. kişilere ödenen tutarın yüzde on beş fazlası,Hizmetin banka bünyesinde karşılanması halinde makul ücret"</t>
@@ -13550,10 +12738,6 @@
           <t>Belge ve Bilgilendirme Ücreti (Ekstre Ücreti)</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>Ekstre gönderim maliyeti kadar ücret tahsil edilmektedir. Gönderim maliyeti değişkenlik göstermektedir</t>
@@ -13576,9 +12760,6 @@
           <t>Kredi Faizi</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr"/>
-      <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
           <t>75.00%</t>
@@ -13606,9 +12787,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr"/>
-      <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
           <t>1.10%</t>
@@ -13636,10 +12814,6 @@
           <t>Belge ve Bilgilendirme Ücreti (Ekstre Ücreti)</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr"/>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>Ekstre gönderim maliyeti kadar ücret tahsil edilmektedir. Gönderim maliyeti değişkenlik göstermektedir</t>
@@ -13662,9 +12836,6 @@
           <t>Kredi Faizi USD</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr"/>
-      <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
           <t>18.01%</t>
@@ -13692,9 +12863,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr"/>
-      <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -13722,9 +12890,6 @@
           <t>Kredi Faizi EUR</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr"/>
-      <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
           <t>16.99%</t>
@@ -13752,9 +12917,6 @@
           <t>Akreditif Açılış Ücreti</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
           <t>4.00%</t>
@@ -13782,13 +12944,11 @@
           <t>Aval Kabul Ücreti</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
           <t>0.25%</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
           <t>0.25%</t>
@@ -13816,14 +12976,11 @@
           <t>Değişiklik Ücreti</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
           <t>100USD</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>*İşlem bazında ve değişiklik anında (ithalat akreditifleri, harici garantiler, kontrgarantiler)*Bedel geldiği anda (ihracat akreditifleri)</t>
@@ -13851,8 +13008,6 @@
           <t>50USD</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
-      <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
           <t>0.10%</t>
@@ -13885,7 +13040,6 @@
           <t>150USD</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
           <t>300USD</t>
@@ -13918,9 +13072,6 @@
           <t>İskonto Ücreti</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
-      <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -13948,14 +13099,11 @@
           <t>İşlem Ücreti</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
           <t>750TL</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
           <t>Dış Ticaret(ithalat/ihracat) işlemleri dosya açılışlarında</t>
@@ -13978,10 +13126,6 @@
           <t>Muhabir Banka Masrafı)</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>işlem bazında ve muhabir borç geçtiğinde</t>
@@ -14009,8 +13153,6 @@
           <t>50USD</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
           <t>0.15%</t>
@@ -14038,14 +13180,11 @@
           <t>Rezerv/Uyuşmazlık Ücreti</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
           <t>150USD</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
           <t>İşlem bazında ve ödeme anında</t>
@@ -14073,8 +13212,6 @@
           <t>100USD</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
           <t>0.75%</t>
@@ -14107,8 +13244,6 @@
           <t>150USD</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
           <t>0.105%</t>
@@ -14136,14 +13271,11 @@
           <t>Uluslararası Fon Transferi Sorgulama/Mesajlaşma Ücreti</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>50TL</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>işlem bazında ve mesajın çekildiği anda</t>
@@ -14166,14 +13298,11 @@
           <t>Vade/Tutar Değişiklik Ücreti</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>100USD</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
           <t>İşlem bazında ve değişiklik anında alınır</t>
@@ -14196,14 +13325,11 @@
           <t>Vade/Tutar Değişikliği Ücreti</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>200USD</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
           <t>işlem bazında ve bedel geldiği anda</t>
@@ -14231,8 +13357,6 @@
           <t>50USD</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
-      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr">
         <is>
           <t>0.15%</t>
@@ -14260,14 +13384,11 @@
           <t>Vesaik İnceleme Ücreti (İhracat Akreditifi)</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
           <t>150USD</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
           <t>işlem bazında ve bedel geldiği anda (ihracat akreditifi)</t>
@@ -14290,10 +13411,6 @@
           <t>Çek İade Ücreti</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
-      <c r="D461" t="inlineStr"/>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr">
         <is>
           <t>Muhabir borç geçtiğinde</t>
@@ -14385,9 +13502,6 @@
           <t>100USD</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>İşlem bazında ve ihbar anında</t>
@@ -14415,13 +13529,11 @@
           <t>4000.00TL</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>4000.00TL</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
           <t>BSMV Hariç</t>
@@ -14449,8 +13561,6 @@
           <t>2600.00TL</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
-      <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -14478,10 +13588,6 @@
           <t>Nakdi Kredi Erken Kapama (Sabit Faizli Döviz Cinsi veya Dövize Endeksli Krediler)</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr"/>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
           <t>6 Ocak 2025 tarihinden itibaren kullandırılan Sabit faizli döviz cinsi veya DEK krediler içinYüzde 3 ile kalan ağırlıklı ortalama vadenin yüzde 0,10’unun toplanması ile ulaşılacaktır. Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir.. Son güncelleme tarihi 06.01.2025</t>
@@ -14504,9 +13610,6 @@
           <t>1 Temmuz 2024 tarihinden itibaren kullandırılan Değişken faizli krediler için</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr"/>
-      <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -14534,10 +13637,6 @@
           <t>1 Temmuz 2024 tarihinden itibaren kullandırılan Sabit faizli Türk Llirası krediler için</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
           <t>Kredinin yıllık bileşik faiz oranının yüzde 5’i ile kalan ağırlıklı ortalama vadenin yüzde 0,20’sinin toplanması ile ulaşılacaktır.Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14560,10 +13659,6 @@
           <t>1 Temmuz 2024 tarihinden itibaren kullandırılan Sabit faizli döviz cinsi veya DEK krediler için</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr"/>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>Yüzde 2 ile kalan ağırlıklı ortalama vadenin yüzde 0,15’inin toplanması ile ulaşılacaktır.Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14586,9 +13681,6 @@
           <t>Nakdi Kredi - Ara/Kısmi Ödeme Ücreti</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
           <t>15.00%</t>
@@ -14616,9 +13708,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti - Kalan Vadesi 24 Aya Kadar Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden 30.06.2024 (Dahil) tarihine kadar Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
           <t>3.00%</t>
@@ -14646,9 +13735,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti - Kalan Vadesi 24 Aya Kadar Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
-      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
           <t>3.00%</t>
@@ -14676,10 +13762,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti - Kalan Vadesi 24 Aydan Uzun Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden 30.06.2024(Dahil) tarihine kadar Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
           <t>Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. %3 üzerine kalan vadesi 24 ayı aşan her bir yıl için %1 eklenerek hesaplanır. Aşan kısımdaki süreler yıla tamamlanır. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14702,9 +13784,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aya Kadar TL Krediler (1.3.2021 Tarihinden 30.06.2024(Dahil) tarihine kadar Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -14732,9 +13811,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti - Kalan Vadesi 24 Aya Kadar Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden Önce Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -14762,10 +13838,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti - Kalan Vadesi 24 Aydan Uzun Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
           <t>Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. %3 üzerine kalan vadesi 24 ayı aşan her bir yıl için %1 eklenerek hesaplanır. Aşan kısımdaki süreler yıla tamamlanır. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14788,9 +13860,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aya Kadar TL Krediler (1.3.2021 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
-      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -14818,9 +13887,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aya Kadar TL Krediler (1.3.2021 Tarihinden Önce Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
           <t>.1.00%</t>
@@ -14848,9 +13914,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aydan Uzun Döviz Cinsi veya Dövize Endeksli Krediler (1.3.2021 Tarihinden Önce Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
           <t>3.00%</t>
@@ -14878,10 +13941,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aydan Uzun TL Krediler (1.3.2021 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
           <t>Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. %2 üzerine kalan vadesi 24 ayı aşan her bir yıl için %1 eklenerek hesaplanır. Aşan kısımdaki süreler yıla tamamlanır. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14904,10 +13963,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aydan Uzun TL Krediler (1.3.2021 Tarihinden 30.06.2024(Dahil) tarihine kadar Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>Kredinin vadesinden önce tamamen kapatılması durumunda kapanan tutar üzerinden alınan ücrettir. %2 üzerine kalan vadesi 24 ayı aşan her bir yıl için %1 eklenerek hesaplanır. Aşan kısımdaki süreler yıla tamamlanır. İşlem bazında ve kapama anında tahsil edilir. BSMV hariçtir</t>
@@ -14930,9 +13985,6 @@
           <t>Nakdi Kredi - Erken Ödeme Ücreti -Kalan Vadesi 24 Aydan Uzun TL Krediler (1.3.2021 Tarihinden Önce Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
-      <c r="D483" t="inlineStr"/>
-      <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr">
         <is>
           <t>2.00%</t>
@@ -14960,9 +14012,6 @@
           <t>Alışveriş Faizi</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr"/>
-      <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -14990,9 +14039,6 @@
           <t>Ek Taksit</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15020,9 +14066,6 @@
           <t>Ekstre Atlat</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15050,9 +14093,6 @@
           <t>Ekstre Taksitlendir</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15080,9 +14120,6 @@
           <t>Fatura</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15110,9 +14147,6 @@
           <t>Gecikme Faizi</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
-      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
           <t>4.55%</t>
@@ -15140,9 +14174,6 @@
           <t>İşlem Erteleme</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15170,9 +14201,6 @@
           <t>İşlem Taksitlendirme</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
-      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15200,9 +14228,6 @@
           <t>Limit Aşım Faizi</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
-      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -15230,9 +14255,6 @@
           <t>Nakit Avans Faizi</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -15260,9 +14282,6 @@
           <t>Nakit Avans Gecikme Faizi</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
-      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
           <t>4.55%</t>
@@ -15290,9 +14309,6 @@
           <t>TNA Faizi</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -15320,9 +14336,6 @@
           <t>Kredi Tahsis Ücreti</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
           <t>0.20%</t>
@@ -15350,15 +14363,11 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
-      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
           <t>5.49%</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -15376,9 +14385,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
           <t>1.10%</t>
@@ -15411,9 +14417,6 @@
           <t>1350.00</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir</t>
@@ -15436,15 +14439,11 @@
           <t>Faiz Oranı</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
-      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
           <t>5.49%</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -15462,9 +14461,6 @@
           <t>Kredi Kullandırım Ücreti</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr">
         <is>
           <t>1.1%</t>
@@ -15497,9 +14493,6 @@
           <t>1350</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr">
         <is>
           <t>Sigorta tutarı yaşa ve teminata göre değişiklik gösterebilir</t>
@@ -15527,13 +14520,11 @@
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
           <t>0.27TL</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr">
         <is>
           <t>BSMV eklenir</t>
@@ -15566,8 +14557,6 @@
           <t>1.15%</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr">
         <is>
           <t>BSMV eklenir</t>
@@ -15590,14 +14579,11 @@
           <t>Basılı Ekstre Ücreti</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>39.11TL</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
           <t>Basılı ekstreler için sayfa başına alınır. BSMV hariç</t>
@@ -15620,14 +14606,11 @@
           <t>Ekstre Gönderim Ücreti</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
           <t>32.43TL</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>Basılı ekstreler için sayfa başına alınır. BSMV hariç</t>
@@ -15660,8 +14643,6 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr">
         <is>
           <t>150.00 TL altı işlemler için Asgari Tutar - 150.00 TL ve üzeri işlemler için Asgari Oran uygulanır. BSMV dahil. Otomatik ödemelerden faiz alınmakta olup aşağıda faiz oranı ayrıca gösterilmiştir</t>
@@ -15760,13 +14741,11 @@
           <t>Kredi Kartına Gelen Uluslararası Para Transferi</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
           <t>3.00%</t>
@@ -15804,8 +14783,6 @@
           <t>1.05%</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr">
         <is>
           <t>Nakit nitekli tüm işlemlerden alınır. Oran + Tutar şeklinde uygulanır. BSMV eklenir</t>
@@ -15838,8 +14815,6 @@
           <t>1.00%</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
       <c r="G512" t="inlineStr">
         <is>
           <t>Nakit nitekli tüm işlemlerden alınır. Oran + Tutar şeklinde uygulanır. BSMV eklenir</t>
@@ -15872,8 +14847,6 @@
           <t>1.12%</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr">
         <is>
           <t>Nakit nitekli tüm işlemlerden alınır. Oran + Tutar şeklinde uygulanır. BSMV eklenir</t>
@@ -15906,8 +14879,6 @@
           <t>1.21%</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr">
         <is>
           <t>Nakit nitekli tüm işlemlerden alınır. Oran + Tutar şeklinde uygulanır. BSMV eklenir</t>
@@ -16014,13 +14985,11 @@
           <t>Nakit Avans Ücreti (Yurtiçi-Garanti BBVA'dan)</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -16048,13 +15017,11 @@
           <t>Taksitli Nakit Avans ve Takistli Para Ücreti</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -16082,14 +15049,11 @@
           <t>Kredi Kartı / Bonus Business</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16112,14 +15076,11 @@
           <t>Kredi Kartı / Bonus Business Troy</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16142,14 +15103,11 @@
           <t>Kredi Kartı / Dragon Bonus Business</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
       <c r="G521" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16172,14 +15130,11 @@
           <t>Kredi Kartı / EASY Bonus</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16202,14 +15157,11 @@
           <t>Kredi Kartı / Bonus Business American Express</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
           <t>2400.00TL</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
       <c r="G523" t="inlineStr">
         <is>
           <t>BSMV dâhil. 12 ay boyunca aylık olarak uygulanır. Companion olarak Bonus Business American Express için yıllık 550 TL, tek başına Bonus Business American Express için yıllık 2400 TL üyelik ücreti uygulanmaktadır. Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16232,14 +15184,11 @@
           <t>Kredi Kartı / Bonus Business American Express (Bağlı)</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
-      <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16262,14 +15211,11 @@
           <t>Kredi Kartı / American Express Business Green</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
           <t>5400.00TL</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16292,14 +15238,11 @@
           <t>Kredi Kartı / American Express Business Gold</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
           <t>7100.00TL</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16322,14 +15265,11 @@
           <t>Kredi Kartı / American Express Corporate Green</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr"/>
-      <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
           <t>5400.00TL</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16352,14 +15292,11 @@
           <t>Kredi Kartı / American Express Corporate Gold</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
           <t>7100.00TL</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16382,14 +15319,11 @@
           <t>Kredi Kartı / Silver Corporate Card</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
-      <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16412,14 +15346,11 @@
           <t>Kredi Kartı / Gold Corporate Card</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
           <t>2400.00TL</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16442,10 +15373,6 @@
           <t>Kredi Kartı / Filo Flexi</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
           <t>Filo Flexi’nin yıllık kart ücreti bulunmamaktadır. BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16468,14 +15395,11 @@
           <t>Kredi Kartı / Filo Kart</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16498,14 +15422,11 @@
           <t>Kredi Kartı / Ortak Kart</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
           <t>2100.00TL</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
           <t>BSMV dâhil.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16528,14 +15449,11 @@
           <t>Kredi Kartı / Miles&amp;Smiles Business</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>BSMV dâhil. Miles&amp;Smiles Business ve Miles&amp;Smiles Business American Express için tek kart ücreti tahsil edilir.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16558,14 +15476,11 @@
           <t>Kredi Kartı / Miles&amp;Smiles Business American Express (Bağlı)</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
           <t>BSMV dâhil. Miles&amp;Smiles Business ve Miles&amp;Smiles Business American Express için tek kart ücreti tahsil edilir.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16588,14 +15503,11 @@
           <t>Kredi Kartı / Shop&amp;Fly Business</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
           <t>BSMV dâhil. Shop&amp;Fly Business ve Shop&amp;Fly Business American Express için tek kart ücreti tahsil edilir.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16618,14 +15530,11 @@
           <t>Kredi Kartı / Shop&amp;Fly Business American Express (Bağlı)</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
           <t>3600.00TL</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
           <t>BSMV dâhil. Shop&amp;Fly Business ve Shop&amp;Fly Business American Express için tek kart ücreti tahsil edilir.Son güncellenme tarihi: 11 Şubat 2026</t>
@@ -16648,15 +15557,11 @@
           <t>Gayrinakdi Kredi - Garantörlük Ücreti</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
       <c r="F538" t="inlineStr">
         <is>
           <t>5.50%</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -16674,9 +15579,6 @@
           <t>Taahhüt Ücreti</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr">
         <is>
           <t>3.00%</t>
@@ -16704,9 +15606,6 @@
           <t>Taahhüte Uymama Ücreti</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr">
         <is>
           <t>5.50%</t>
@@ -16734,14 +15633,11 @@
           <t>Bonus</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16764,14 +15660,11 @@
           <t>Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16794,14 +15687,11 @@
           <t>BJK Bonus</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16824,14 +15714,11 @@
           <t>BJK Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16854,14 +15741,11 @@
           <t>BJK Bonus Gold</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16884,14 +15768,11 @@
           <t>BJK Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16914,14 +15795,11 @@
           <t>BJK Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16944,14 +15822,11 @@
           <t>BJK Bonus Platinum</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -16974,14 +15849,11 @@
           <t>Aynalı Bonus</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17004,14 +15876,11 @@
           <t>Aynalı Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17034,14 +15903,11 @@
           <t>Bonus Trink Saat</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
           <t>79.50TL</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17064,14 +15930,11 @@
           <t>Bonus Trink Saat-Ek Kart</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
           <t>39.00TL</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17094,14 +15957,11 @@
           <t>Bonus Trink Sticker</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
           <t>79.50TL</t>
         </is>
       </c>
-      <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17124,14 +15984,11 @@
           <t>Bonus Trink Sticker-Ek Kart</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
           <t>39.00TL</t>
         </is>
       </c>
-      <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17154,14 +16011,11 @@
           <t>Bonus Trink</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr"/>
-      <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17184,14 +16038,11 @@
           <t>Bonus Trink-Ek Kart</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr"/>
-      <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17214,14 +16065,11 @@
           <t>Bonus Trink Anahtarlık</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr"/>
-      <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr">
         <is>
           <t>79.50TL</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17244,14 +16092,11 @@
           <t>Bonus Trink Anahtarlık-Ek Kart</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr"/>
-      <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
           <t>39.00TL</t>
         </is>
       </c>
-      <c r="F558" t="inlineStr"/>
       <c r="G558" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17274,14 +16119,11 @@
           <t>Bonus Platinum Amex</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr"/>
-      <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17304,14 +16146,11 @@
           <t>Bonus Platinum Amex-Ek Kart</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
-      <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
           <t>BSMV dâhil. Ürün başvuruya açık değildir</t>
@@ -17334,14 +16173,11 @@
           <t>GS Bonus</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
-      <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17364,14 +16200,11 @@
           <t>GS Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
-      <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17394,14 +16227,11 @@
           <t>GS Bonus Gold</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17424,14 +16254,11 @@
           <t>GS Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr"/>
-      <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17454,14 +16281,11 @@
           <t>GS Bonus Platinum</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr"/>
-      <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17484,14 +16308,11 @@
           <t>GS Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17514,14 +16335,11 @@
           <t>Altın Bonus</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17544,14 +16362,11 @@
           <t>Altın Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr"/>
-      <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17574,14 +16389,11 @@
           <t>Trabzonspor Bonus</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr"/>
       <c r="G569" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17604,14 +16416,11 @@
           <t>Trabzonspor Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17634,14 +16443,11 @@
           <t>Trabzonspor Bonus Gold</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17664,14 +16470,11 @@
           <t>Trabzonspor Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr"/>
       <c r="G572" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17694,14 +16497,11 @@
           <t>Trabzonspor Bonus Platinum</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr"/>
       <c r="G573" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17724,14 +16524,11 @@
           <t>Trabzonspor Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17754,14 +16551,11 @@
           <t>Bonus American Express</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -17784,14 +16578,11 @@
           <t>Bonus American Express-Ek Kart</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -17814,14 +16605,11 @@
           <t>Bonus American Express-Bonus Companion</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
           <t>321.50TL</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -17844,14 +16632,11 @@
           <t>Bonus American Express-Bonus Companion-Ek Kart</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
           <t>155.50TL</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -17874,14 +16659,11 @@
           <t>Bonus Gold</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
       <c r="G579" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17904,14 +16686,11 @@
           <t>Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -17934,14 +16713,11 @@
           <t>Bonus Platinum Biyometrik</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
           <t>3396.50TL</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -17964,14 +16740,11 @@
           <t>Bonus Platinum Dinamik</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
           <t>3396.50TL</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -17994,14 +16767,11 @@
           <t>Bonus Platinum</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr"/>
       <c r="G583" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18024,14 +16794,11 @@
           <t>Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18054,14 +16821,11 @@
           <t>Aynalı Gold</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr"/>
       <c r="G585" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18084,14 +16848,11 @@
           <t>Aynalı Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18114,14 +16875,11 @@
           <t>Aynalı Platinum</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr"/>
       <c r="G587" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18144,14 +16902,11 @@
           <t>Aynalı Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F588" t="inlineStr"/>
       <c r="G588" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18174,14 +16929,11 @@
           <t>Şeffaf Bonus</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr"/>
       <c r="G589" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18204,14 +16956,11 @@
           <t>Şeffaf Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr"/>
       <c r="G590" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18234,14 +16983,11 @@
           <t>Şeffaf Bonus Gold</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
       <c r="G591" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18264,14 +17010,11 @@
           <t>Şeffaf Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
       <c r="G592" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18294,14 +17037,11 @@
           <t>Şeffaf Bonus Platinum</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr"/>
-      <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr"/>
       <c r="G593" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18324,14 +17064,11 @@
           <t>Şeffaf Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr"/>
       <c r="G594" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18354,14 +17091,11 @@
           <t>Çevreci Bonus</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F595" t="inlineStr"/>
       <c r="G595" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18384,14 +17118,11 @@
           <t>Çevreci Gold</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F596" t="inlineStr"/>
       <c r="G596" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18414,14 +17145,11 @@
           <t>Çevreci Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F597" t="inlineStr"/>
       <c r="G597" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18444,14 +17172,11 @@
           <t>Çevreci Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18474,14 +17199,11 @@
           <t>Çevreci Platinum</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F599" t="inlineStr"/>
       <c r="G599" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18504,14 +17226,11 @@
           <t>Çevreci Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18534,14 +17253,11 @@
           <t>Bonus Trink Gold</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F601" t="inlineStr"/>
       <c r="G601" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18564,14 +17280,11 @@
           <t>Bonus Trink Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18654,14 +17367,11 @@
           <t>Fenerbahçe Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18714,14 +17424,11 @@
           <t>Fenerbahçe Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F607" t="inlineStr"/>
       <c r="G607" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18774,14 +17481,11 @@
           <t>Fenerbahçe Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18804,14 +17508,11 @@
           <t>Bonus Diji</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F610" t="inlineStr"/>
       <c r="G610" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18834,14 +17535,11 @@
           <t>Bonus Gold Diji</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr"/>
       <c r="G611" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18864,14 +17562,11 @@
           <t>Bonus Platinum Diji</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
-      <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -18894,8 +17589,6 @@
           <t>Bonus Flexi</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -18906,7 +17599,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr"/>
       <c r="H613" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -18924,8 +17616,6 @@
           <t>Bonus Flexi - Ek Kart</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -18936,7 +17626,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr"/>
       <c r="H614" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -18954,8 +17643,6 @@
           <t>Bonus Genç</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -18966,7 +17653,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -18984,14 +17670,11 @@
           <t>Emeklilere Bonus</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
-      <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F616" t="inlineStr"/>
       <c r="G616" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19014,14 +17697,11 @@
           <t>Emeklilere Bonus - Ek Kart</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F617" t="inlineStr"/>
       <c r="G617" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -19044,14 +17724,11 @@
           <t>Bonus Cool</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr"/>
-      <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -19074,14 +17751,11 @@
           <t>Bonus Cool- Ek Kart</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F619" t="inlineStr"/>
       <c r="G619" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -19524,14 +18198,11 @@
           <t>American Express Card</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
           <t>3395.00TL</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr"/>
       <c r="G634" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19554,14 +18225,11 @@
           <t>American Express Card-Ek Kart</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
           <t>1112.00TL</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr"/>
       <c r="G635" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19584,14 +18252,11 @@
           <t>American Express Gold Card</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
           <t>6795.00TL</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr"/>
       <c r="G636" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19614,14 +18279,11 @@
           <t>American Express Gold Card-Ek Kart</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr">
         <is>
           <t>3395.00TL</t>
         </is>
       </c>
-      <c r="F637" t="inlineStr"/>
       <c r="G637" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19644,14 +18306,11 @@
           <t>American Express Platinum Card</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
           <t>13695.00TL</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr"/>
       <c r="G638" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19674,14 +18333,11 @@
           <t>American Express Platinum Card-Ek Kart</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
           <t>6845.00TL</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr"/>
       <c r="G639" t="inlineStr">
         <is>
           <t>BSMV dahil</t>
@@ -19704,14 +18360,11 @@
           <t>American Express Black Card</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
           <t>97130.00TL</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr"/>
       <c r="G640" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -19734,14 +18387,11 @@
           <t>American Express Black Card-Ek Kart</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
           <t>48560.00TL</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr"/>
       <c r="G641" t="inlineStr">
         <is>
           <t>BSMV dâhil</t>
@@ -19764,15 +18414,11 @@
           <t>The Platinum Card</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
           <t>13695.00TL</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -19790,15 +18436,11 @@
           <t>The Platinum Card - Ek Kart</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
           <t>6845.00TL</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -19816,15 +18458,11 @@
           <t>Metal The Platinum Card</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
           <t>20310.00TL</t>
         </is>
       </c>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -19842,15 +18480,11 @@
           <t>Metal The Platinum Card - Ek Kart</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
           <t>10155.00TL</t>
         </is>
       </c>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -19868,14 +18502,11 @@
           <t>Flexi</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
           <t>3168.00TL</t>
         </is>
       </c>
-      <c r="F646" t="inlineStr"/>
       <c r="G646" t="inlineStr">
         <is>
           <t>Minimum 0.00 TL (BSMV dahil)</t>
@@ -19898,14 +18529,11 @@
           <t>Flexi-Ek Kart</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
           <t>1584.00TL</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr"/>
       <c r="G647" t="inlineStr">
         <is>
           <t>Asıl kart ücretinin yarısıdır (BSMV dahil)</t>
@@ -19928,14 +18556,11 @@
           <t>Money Bonus</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
           <t>1101.00TL</t>
         </is>
       </c>
-      <c r="F648" t="inlineStr"/>
       <c r="G648" t="inlineStr">
         <is>
           <t>BSMV dahil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -19958,14 +18583,11 @@
           <t>Money Bonus-Ek Kart</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
           <t>548.00TL</t>
         </is>
       </c>
-      <c r="F649" t="inlineStr"/>
       <c r="G649" t="inlineStr">
         <is>
           <t>BSMV dahil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -19988,14 +18610,11 @@
           <t>Money Bonus Gold</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
-      <c r="D650" t="inlineStr"/>
       <c r="E650" t="inlineStr">
         <is>
           <t>1282.00TL</t>
         </is>
       </c>
-      <c r="F650" t="inlineStr"/>
       <c r="G650" t="inlineStr">
         <is>
           <t>BSMV dahil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -20018,14 +18637,11 @@
           <t>Money Bonus Gold-Ek Kart</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr">
         <is>
           <t>637.00TL</t>
         </is>
       </c>
-      <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr">
         <is>
           <t>BSMV dâhil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -20048,14 +18664,11 @@
           <t>Money Bonus Platinum</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr"/>
-      <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr">
         <is>
           <t>1439.50TL</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr"/>
       <c r="G652" t="inlineStr">
         <is>
           <t>BSMV dâhil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -20078,14 +18691,11 @@
           <t>Money Bonus Platinum-Ek Kart</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr">
         <is>
           <t>716.50TL</t>
         </is>
       </c>
-      <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr">
         <is>
           <t>BSMV dâhil. Son güncellenme tarihi: 11 Şubat 2025</t>
@@ -20108,8 +18718,6 @@
           <t>Paracard</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -20120,7 +18728,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -20138,8 +18745,6 @@
           <t>Paracard - Ek Kart</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -20150,7 +18755,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr"/>
       <c r="H655" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -20168,10 +18772,6 @@
           <t>Paracard Trink</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
-      <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -20194,8 +18794,6 @@
           <t>Paracard Trink - Ek Kart</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -20206,7 +18804,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr"/>
       <c r="H657" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -20224,10 +18821,6 @@
           <t>GS Paracard Debit</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr"/>
-      <c r="F658" t="inlineStr"/>
       <c r="G658" t="inlineStr">
         <is>
           <t>BSMV Dahil</t>
@@ -20250,19 +18843,16 @@
           <t>GS Paracard Debit - Ek Kart</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr"/>
       <c r="F659" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -20280,14 +18870,11 @@
           <t>iGaranti BBVA Kredi Kartı</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr">
         <is>
           <t>322.50TL</t>
         </is>
       </c>
-      <c r="F660" t="inlineStr"/>
       <c r="G660" t="inlineStr">
         <is>
           <t>Ek Kart ücreti asıl kartın yarısıdır. BSMV dahildir</t>
@@ -20310,13 +18897,11 @@
           <t>Alışveriş Faizi</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr"/>
       <c r="F661" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -20344,9 +18929,6 @@
           <t>Nakit Avans Faizi</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
       <c r="F662" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -20374,9 +18956,6 @@
           <t>Gecikme Faizi</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr"/>
-      <c r="E663" t="inlineStr"/>
       <c r="F663" t="inlineStr">
         <is>
           <t>3.55%</t>
@@ -20404,13 +18983,11 @@
           <t>Limit Aşım Faizi</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr"/>
       <c r="F664" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -20438,9 +19015,6 @@
           <t>Taksitli Nakit Avans Faizi</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
       <c r="F665" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -20468,9 +19042,6 @@
           <t>Taksitli Nakit Avans Gecikme Faizi</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
           <t>4.55%</t>
@@ -20498,9 +19069,6 @@
           <t>Ekstre Atlat</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
       <c r="F667" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -20528,13 +19096,11 @@
           <t>İşlem Atlat</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr">
         <is>
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr"/>
       <c r="F668" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -20562,13 +19128,11 @@
           <t>İşlem Taksitlendir</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr"/>
       <c r="F669" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -20596,13 +19160,11 @@
           <t>Ekstre Taksitlendir</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E670" t="inlineStr"/>
       <c r="F670" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -20630,13 +19192,11 @@
           <t>Ek Taksit</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr"/>
       <c r="F671" t="inlineStr">
         <is>
           <t>4.50%</t>
@@ -20664,13 +19224,11 @@
           <t>Otomatik Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
-      <c r="E672" t="inlineStr"/>
       <c r="F672" t="inlineStr">
         <is>
           <t>4.25%</t>
@@ -20698,14 +19256,11 @@
           <t>POS yazılım/donanım/bakım ücreti-Fiziki POS</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
           <t>995.00TL</t>
         </is>
       </c>
-      <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr">
         <is>
           <t>Aylık olarak alınır. BSMV dahildir. Ücretler terminal başına alınır ve cihazlara verilen kurulum, değişim, yazılım güncelleme, bakım ve onarım hizmetlerini kapsar. Ücretler terminal modeline göre değişmekte olup, GPRS, ÖKC, ve Sabit POS cihazlar için en yüksek ücret 995 TL'dir</t>
@@ -20728,14 +19283,11 @@
           <t>POS yazılım/donanım/bakım ücreti-Fiziki POS-e-Faturalı Cihaz</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr">
         <is>
           <t>Aylık olarak alınır. BSMV dahildir. Yalnızca e-faturalı cihazlar için geçerlidir</t>
@@ -20758,14 +19310,11 @@
           <t>POS yazılım/donanım/bakım ücreti-Sanal POS</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr">
         <is>
           <t>9900.00TL</t>
         </is>
       </c>
-      <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr">
         <is>
           <t>Yıllık olarak alınır. BSMV dahildir. Ücretler terminal başına alınır ve cihazlara verilen kurulum, yazılım güncelleme, bakım ve onarım hizmetlerini kapsar</t>
@@ -20788,14 +19337,11 @@
           <t>Kayıp/hasarlı pos ve aksesuar bedeli</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr">
         <is>
           <t>10380.00TL</t>
         </is>
       </c>
-      <c r="F676" t="inlineStr"/>
       <c r="G676" t="inlineStr">
         <is>
           <t>BSMV dahildir</t>
@@ -20818,9 +19364,6 @@
           <t>2 Taksit</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr"/>
       <c r="F677" t="inlineStr">
         <is>
           <t>5.34%</t>
@@ -20848,9 +19391,6 @@
           <t>3 Taksit</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr"/>
-      <c r="D678" t="inlineStr"/>
-      <c r="E678" t="inlineStr"/>
       <c r="F678" t="inlineStr">
         <is>
           <t>7.12%</t>
@@ -20878,9 +19418,6 @@
           <t>4 Taksit</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
       <c r="F679" t="inlineStr">
         <is>
           <t>8.9%</t>
@@ -20908,9 +19445,6 @@
           <t>5 Taksit</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
       <c r="F680" t="inlineStr">
         <is>
           <t>10.68%</t>
@@ -20938,9 +19472,6 @@
           <t>6 Taksit</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
           <t>12.46%</t>
@@ -20968,9 +19499,6 @@
           <t>7 Taksit</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
-      <c r="E682" t="inlineStr"/>
       <c r="F682" t="inlineStr">
         <is>
           <t>14.24%</t>
@@ -20998,9 +19526,6 @@
           <t>8 Taksit</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
           <t>16.02%</t>
@@ -21028,9 +19553,6 @@
           <t>9 Taksit</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
-      <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
           <t>17.8%</t>
@@ -21058,9 +19580,6 @@
           <t>10 Taksit</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
-      <c r="E685" t="inlineStr"/>
       <c r="F685" t="inlineStr">
         <is>
           <t>19.58%</t>
@@ -21088,9 +19607,6 @@
           <t>11 Taksit</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr"/>
       <c r="F686" t="inlineStr">
         <is>
           <t>21.36%</t>
@@ -21118,9 +19634,6 @@
           <t>12 Taksit</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr">
         <is>
           <t>23.14%</t>
@@ -21148,9 +19661,6 @@
           <t>13 Taksit</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
           <t>24.92%</t>
@@ -21178,9 +19688,6 @@
           <t>14 Taksit</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
       <c r="F689" t="inlineStr">
         <is>
           <t>26.7%</t>
@@ -21208,9 +19715,6 @@
           <t>15 Taksit</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
       <c r="F690" t="inlineStr">
         <is>
           <t>28.48%</t>
@@ -21238,9 +19742,6 @@
           <t>16 Taksit</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
           <t>30.26%</t>
@@ -21268,9 +19769,6 @@
           <t>17 Taksit</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
-      <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr">
         <is>
           <t>32.04%</t>
@@ -21298,9 +19796,6 @@
           <t>18 Taksit</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
-      <c r="E693" t="inlineStr"/>
       <c r="F693" t="inlineStr">
         <is>
           <t>33.82%</t>
@@ -21328,9 +19823,6 @@
           <t>Garanti BBVA Kredi Kartları</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
-      <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr">
         <is>
           <t>3.56%</t>
@@ -21358,9 +19850,6 @@
           <t>Garanti BBVA Banka Kartları</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
-      <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr">
         <is>
           <t>1.04%</t>
@@ -21388,9 +19877,6 @@
           <t>Yurtiçi Diğer Banka - Kredi Kartları</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr"/>
-      <c r="D696" t="inlineStr"/>
-      <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr">
         <is>
           <t>3.56%</t>
@@ -21418,9 +19904,6 @@
           <t>Yurtiçi Diğer Banka - Banka Kartları</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr">
         <is>
           <t>1.04%</t>
@@ -21448,9 +19931,6 @@
           <t>Yurtdışı Kartlar</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
           <t>1.90%</t>
@@ -21478,14 +19958,11 @@
           <t>Ekstre Gönderim Ücreti</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr">
         <is>
           <t>45.00TL</t>
         </is>
       </c>
-      <c r="F699" t="inlineStr"/>
       <c r="G699" t="inlineStr">
         <is>
           <t>Basılı ekstre ücretleri 20 grama kadar 45 TL, 20-50 gram arası 55 TL olarak ücretlendirilir. BSMV dahildir. Son Güncellenme Tarihi: 4 Şubat 2026</t>
@@ -21508,9 +19985,6 @@
           <t>Bloke Çözüm Ücreti- Kredi Kartları</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
-      <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr">
         <is>
           <t>0.0890%</t>
@@ -21538,9 +20012,6 @@
           <t>Bloke Çözüm Ücreti- Banka Kartları</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
-      <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr">
         <is>
           <t>0.0693%</t>
@@ -21568,9 +20039,6 @@
           <t>Bloke Çözüm Ücreti- Yurtdışı Kartları</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
-      <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr">
         <is>
           <t>0.0475%</t>
@@ -21598,14 +20066,11 @@
           <t>Aynalı Bonus</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr"/>
-      <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
           <t>130.00TL</t>
         </is>
       </c>
-      <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr">
         <is>
           <t>Mevcut Bonus kartınızı Aynalı Bonus ile değiştirmek için ücret ödenir (BSMV dâhil)</t>
@@ -21638,8 +20103,6 @@
           <t>1.00%</t>
         </is>
       </c>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
       <c r="G704" t="inlineStr">
         <is>
           <t>Karttan Havale/EFT işlemlerinde işlem tutarı üzerinden %1 oranında nakit avans işlem ücreti uygulanır (BSMV Hariç). Buna ek olarak,Garanti BBVA Mobil ve İnternet Bankacılığı’ndan yapılan işlemlerde:EFT işlemleri için 0-8.300 TL arasına 7,97 TL, 8.300-399.000 TL arasına 15,96 TL, 399.000 TL üzerine ise 199,41 TL EFT ücreti, Havale işlemleri için 0-8.300 TL arasına 3,99 TL, 8.300-399.000 TL arasına 7,98 TL, 399.000 TL üzerine ise 99,71 TL havale ücreti alınacaktır (BSMV hariç).Garanti BBVA ATM’lerinden yapılan işlemlerde:EFT işlemleri için 0-8.300 TL arasına 27,84 TL, 8.300-399.000 TL arasına 55,69 TL, 399.000 TL üzerine ise 398,83 TL EFT ücreti, Havale işlemleri için 0-8.300 TL arasına 13,92 TL, 8.300-399.000 TL arasına 27,85 TL, 399.000 TL üzerine ise 199,42 TL havale ücreti alınacaktır (BSMV hariç).Ayrıca Karttan Havale/EFT kullanımlarında işlem tarihinden itibaren günlük nakit faizi işletilir</t>
@@ -21662,14 +20125,11 @@
           <t>Bonus Trink Saat</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>70TL</t>
         </is>
       </c>
-      <c r="F705" t="inlineStr"/>
       <c r="G705" t="inlineStr">
         <is>
           <t>Tek seferlik ürün ücreti BSMV dâhil</t>
@@ -21692,14 +20152,11 @@
           <t>Bonus Şeffaf Card</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr"/>
-      <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr">
         <is>
           <t>130.00TL</t>
         </is>
       </c>
-      <c r="F706" t="inlineStr"/>
       <c r="G706" t="inlineStr">
         <is>
           <t>Mevcut Bonus kartınızı Şeffaf Bonus ile değiştirmek için ücret ödenir (BSMV dâhil)</t>
@@ -21732,8 +20189,6 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E707" t="inlineStr"/>
-      <c r="F707" t="inlineStr"/>
       <c r="G707" t="inlineStr">
         <is>
           <t>150 TL altı işlemler için Asgari Tutar , - 150 TL ve üzerindeki işlemler için Asgari Oran uygulanır</t>
@@ -21756,7 +20211,6 @@
           <t>Kredi Kartı Geçmiş Ekstre Üc.</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr"/>
       <c r="D708" t="inlineStr">
         <is>
           <t>0.00%</t>
@@ -21804,8 +20258,6 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="E709" t="inlineStr"/>
-      <c r="F709" t="inlineStr"/>
       <c r="G709" t="inlineStr">
         <is>
           <t>100 TL altı işlemler için Asgari Tutar , 100 TL ve üzerindeki işlemler için Asgari Oran uygulanır</t>
@@ -21828,9 +20280,6 @@
           <t>Kur Dönüşüm Hizmeti ( POS DCC )</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr">
         <is>
           <t>5.00%</t>
@@ -21863,14 +20312,11 @@
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="F711" t="inlineStr"/>
-      <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -21893,13 +20339,11 @@
           <t>750.00TL</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr">
         <is>
           <t>750.00TL</t>
         </is>
       </c>
-      <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr">
         <is>
           <t>BSMV dahildir. 6 aylık dönemlerde, yılda iki kere tahsilat yapılmaktadır.Yabancı para cinsi vadesiz hesaplardan yapılacak tahsilatlarda 750 TL muadili ücret tahsilat anında; açıklanan en güncel merkez bankası döviz kuruna göre belirlenecektir</t>
@@ -21927,13 +20371,11 @@
           <t>52.48TL</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr">
         <is>
           <t>52.48TL</t>
         </is>
       </c>
-      <c r="F713" t="inlineStr"/>
       <c r="G713" t="inlineStr">
         <is>
           <t>Avans hesabı olan müşterilerimizden, Avans hesaplarını kullandıkları aylar dahilinde aylık tahsilat yapılmaktadır. BSMV dahildir</t>
@@ -21961,13 +20403,11 @@
           <t>52.48TL</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr">
         <is>
           <t>52.48TL</t>
         </is>
       </c>
-      <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr">
         <is>
           <t>Talep edilen ekstre başına tahsilat yapılmaktadır. BSMV dahildir</t>
@@ -21995,13 +20435,11 @@
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr">
         <is>
           <t>Muadili ücret tahsil edilmektedir. Talep edilen ekstre başına tahsilat yapılmaktadır. BSMV dahildir</t>
@@ -22024,13 +20462,11 @@
           <t>Garanti BBVA eTrader</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E716" t="inlineStr"/>
       <c r="F716" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22058,13 +20494,11 @@
           <t>Garanti BBVA İnternet</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E717" t="inlineStr"/>
       <c r="F717" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22092,13 +20526,11 @@
           <t>Garanti BBVA Mobil</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22126,13 +20558,11 @@
           <t>Garanti BBVA Müşteri İletişim Merkezi</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22160,13 +20590,11 @@
           <t>Garanti BBVA Yatırım Şubesi</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22199,13 +20627,11 @@
           <t>250.00TL</t>
         </is>
       </c>
-      <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
           <t>250.00TL</t>
         </is>
       </c>
-      <c r="F721" t="inlineStr"/>
       <c r="G721" t="inlineStr">
         <is>
           <t>Hisse senedi hesaplarından 6 ayda bir 250 TL (BSMV dahil) (yıllık 500 TL (BSMV dahil)) hesap bakım ücreti tahsil edilmektedir. Yıllık hesap bakım ücreti hisse senedi satış takas tutarı içerisinden tahsil edilir. İlgili tutarlarda değişiklik olması durumunda internet sayfamızda güncellenmektedir</t>
@@ -22228,13 +20654,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 0-500.000 TL</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
           <t>0.199000%</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr"/>
       <c r="F722" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22262,13 +20686,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 500.001-1.000.000 TL</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
           <t>0.195000%</t>
         </is>
       </c>
-      <c r="E723" t="inlineStr"/>
       <c r="F723" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22296,13 +20718,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 1.000.001 – 2.500.000 TL</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
           <t>0.190000%</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr"/>
       <c r="F724" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22330,13 +20750,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 2.500.001 – 5.000.000 TL</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
           <t>0.180000%</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr"/>
       <c r="F725" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22364,13 +20782,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 5.000.001 – 7.500.000 TL</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
           <t>0.170000%</t>
         </is>
       </c>
-      <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22398,13 +20814,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 7.500.001 – 10.000.000 TL</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr">
         <is>
           <t>0.160000%</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22432,13 +20846,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 10.000.001 – 12.500.000 TL</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
           <t>0.150000%</t>
         </is>
       </c>
-      <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22466,13 +20878,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 12.500.001 – 17.500.000 TL</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
           <t>0.140000%</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr"/>
       <c r="F729" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22500,13 +20910,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 17.500.001 – 25.000.000 TL</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
           <t>0.120000%</t>
         </is>
       </c>
-      <c r="E730" t="inlineStr"/>
       <c r="F730" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22534,13 +20942,11 @@
           <t>Son 3 Aylık Ortalama İşlem Hacmi 25.000.000 +</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
           <t>0.090000%</t>
         </is>
       </c>
-      <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr">
         <is>
           <t>0.320000%</t>
@@ -22578,7 +20984,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -22616,7 +21021,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="E733" t="inlineStr"/>
       <c r="F733" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -22654,7 +21058,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="E734" t="inlineStr"/>
       <c r="F734" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -22692,7 +21095,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="E735" t="inlineStr"/>
       <c r="F735" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -22730,7 +21132,6 @@
           <t>0.084%</t>
         </is>
       </c>
-      <c r="E736" t="inlineStr"/>
       <c r="F736" t="inlineStr">
         <is>
           <t>0.0105%</t>
@@ -22758,14 +21159,11 @@
           <t>Garanti Yatırım Şubesi</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
           <t>9.900000%</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr"/>
-      <c r="F737" t="inlineStr"/>
       <c r="G737" t="inlineStr">
         <is>
           <t>Oranlar aylık olup %5.00 BSMV eklenmektedir. Ödemede gecikme olması durumunda kredi faizine ek olarak, aylık (yıllık) TCMB tarafından belirlenen azami temerrüt faiz oranı eklenecektir</t>
@@ -22788,14 +21186,11 @@
           <t>İnternet</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
           <t>9.900000%</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
       <c r="G738" t="inlineStr">
         <is>
           <t>Oranlar aylık olup %5.00 BSMV eklenmektedir. Ödemede gecikme olması durumunda kredi faizine ek olarak, aylık (yıllık) TCMB tarafından belirlenen azami temerrüt faiz oranı eklenecektir</t>
@@ -22818,13 +21213,11 @@
           <t>Garanti Portföy Ağustos 2024 Serbest (Döviz-ABD Doları) Fon</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr"/>
       <c r="F739" t="inlineStr">
         <is>
           <t>2%</t>
@@ -22852,13 +21245,11 @@
           <t>Garanti Portföy Şubat 2025 Serbest (Döviz-ABD Doları) Fon</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E740" t="inlineStr"/>
       <c r="F740" t="inlineStr">
         <is>
           <t>2%</t>
@@ -22886,13 +21277,11 @@
           <t>Garanti Portföy Haziran 2025 Serbest (Döviz-Avro) Fon</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E741" t="inlineStr"/>
       <c r="F741" t="inlineStr">
         <is>
           <t>2%</t>
@@ -22920,13 +21309,11 @@
           <t>Garanti Portföy Ocak 2026 Serbest (Döviz-ABD Doları) Fon</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
           <t>2%</t>
@@ -22954,13 +21341,11 @@
           <t>Garanti Portföy Ekim 2026 Serbest (Döviz-ABD Doları) Fon</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
           <t>2%</t>
@@ -22988,19 +21373,16 @@
           <t>Varant Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr">
         <is>
           <t>0.08%</t>
         </is>
       </c>
-      <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr">
         <is>
           <t>0.08%</t>
         </is>
       </c>
-      <c r="G744" t="inlineStr"/>
       <c r="H744" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23018,19 +21400,16 @@
           <t>ÖSBA Kupon Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="E745" t="inlineStr"/>
       <c r="F745" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr"/>
       <c r="H745" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23048,13 +21427,11 @@
           <t>Açık Hisse Sermaye Artırım (Bedelli)</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
           <t>0.025%</t>
         </is>
       </c>
-      <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr">
         <is>
           <t>0.025%</t>
@@ -23082,13 +21459,11 @@
           <t>Açık Hisse Sermaye Artırım (Bedelsiz)</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr">
         <is>
           <t>0.025%</t>
         </is>
       </c>
-      <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr">
         <is>
           <t>0.025%</t>
@@ -23116,13 +21491,11 @@
           <t>Kapalı Hisse Sermaye Artırım Bedeli</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr">
         <is>
           <t>0.01%</t>
@@ -23150,13 +21523,11 @@
           <t>Kapalı Hisse Sermaye Artırım Bedelsiz</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr">
         <is>
           <t>0.01%</t>
@@ -23184,8 +21555,6 @@
           <t>OSBA Kupon Ayrıştırma Ücreti</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -23196,7 +21565,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G750" t="inlineStr"/>
       <c r="H750" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23214,8 +21582,6 @@
           <t>BYF Alım Satım Ücreti</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -23226,7 +21592,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G751" t="inlineStr"/>
       <c r="H751" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23244,13 +21609,11 @@
           <t>Açık Hisse Sermaye Azaltım Ücreti</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
           <t>0.025%</t>
         </is>
       </c>
-      <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
           <t>0.025%</t>
@@ -23278,10 +21641,6 @@
           <t>Hesap Bakım Ücreti</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr"/>
-      <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
           <t>1.000-TL ve üzeri piyasa değerli saklama bakiyesi günlük 0,11-TL</t>
@@ -23304,13 +21663,11 @@
           <t>Kapalı Hisse Sermaye Azaltım Ücreti</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
           <t>0.01%</t>
@@ -23338,19 +21695,16 @@
           <t>ÖSBA Kupon İtfa Ücreti</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr"/>
       <c r="D755" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23368,19 +21722,16 @@
           <t>Açık Hisse Temettü Ücreti</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
           <t>0.025%</t>
         </is>
       </c>
-      <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
           <t>0.025%</t>
         </is>
       </c>
-      <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23398,19 +21749,16 @@
           <t>Kapalı Hisse Temettü Ücreti</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
           <t>0.005%</t>
         </is>
       </c>
-      <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
           <t>0.005%</t>
         </is>
       </c>
-      <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23438,7 +21786,6 @@
           <t>0.001%</t>
         </is>
       </c>
-      <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
           <t>0.001%</t>
@@ -23476,8 +21823,6 @@
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E759" t="inlineStr"/>
-      <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr">
         <is>
           <t>İşlem Piyasa Değeri</t>
@@ -23505,9 +21850,6 @@
           <t>139.21TL</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr"/>
-      <c r="E760" t="inlineStr"/>
-      <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr">
         <is>
           <t>İşlem sayısı</t>
@@ -23535,9 +21877,6 @@
           <t>1.39TL</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
-      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
           <t>İşlem sayısı</t>
@@ -23560,8 +21899,6 @@
           <t>EMKT Depo Devri</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -23572,7 +21909,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23595,9 +21931,6 @@
           <t>17.75TL</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
-      <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
           <t>Açılan hesap başına</t>
@@ -23625,7 +21958,6 @@
           <t>13.05TL</t>
         </is>
       </c>
-      <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr">
         <is>
           <t>25.78TL</t>
@@ -23663,7 +21995,6 @@
           <t>1.38TL</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr">
         <is>
           <t>6.90TL</t>
@@ -23696,8 +22027,6 @@
           <t>Uluslararası Gönderim Ücreti</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -23708,7 +22037,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23726,8 +22054,6 @@
           <t>Uluslararası Kabul Ücreti</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr">
         <is>
           <t>0.00TL</t>
@@ -23738,7 +22064,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -23756,13 +22081,11 @@
           <t>Yasaklı Paya Dönüşüm Ücreti</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr">
         <is>
           <t>0.05%</t>
         </is>
       </c>
-      <c r="E768" t="inlineStr"/>
       <c r="F768" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -23790,9 +22113,6 @@
           <t>Yasaklıdan Kapalıya Dönüşüm Ücreti</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
       <c r="F769" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -23820,8 +22140,6 @@
           <t>Saklama Takasbank Şartlı Virman</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr">
         <is>
           <t>4.00%</t>
@@ -23854,13 +22172,11 @@
           <t>Açık Hisse Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr">
         <is>
           <t>0.08%</t>
         </is>
       </c>
-      <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr">
         <is>
           <t>0.08%</t>
@@ -23888,13 +22204,11 @@
           <t>Kapalı Hisse Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr"/>
       <c r="D772" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E772" t="inlineStr"/>
       <c r="F772" t="inlineStr">
         <is>
           <t>0.01%</t>
@@ -23922,13 +22236,11 @@
           <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi Yatırım Fonları Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr">
         <is>
           <t>0.005%</t>
         </is>
       </c>
-      <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr">
         <is>
           <t>0.005%</t>
@@ -23956,13 +22268,11 @@
           <t>Diğer Yatırım Fonları Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr"/>
       <c r="D774" t="inlineStr">
         <is>
           <t>0.01%</t>
         </is>
       </c>
-      <c r="E774" t="inlineStr"/>
       <c r="F774" t="inlineStr">
         <is>
           <t>0.01%</t>
@@ -23990,19 +22300,16 @@
           <t>ÖSBA Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr">
         <is>
           <t>0.05%</t>
         </is>
       </c>
-      <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr">
         <is>
           <t>0.05%</t>
         </is>
       </c>
-      <c r="G775" t="inlineStr"/>
       <c r="H775" t="inlineStr">
         <is>
           <t>31.07.2026</t>
@@ -24020,14 +22327,11 @@
           <t>MKK Nezdinde Adına İlk Kez Sicil Açılan Yatırımcıların Bilgilendirilmesi</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr">
         <is>
           <t>8.00TL</t>
         </is>
       </c>
-      <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
           <t>Yatırımcıya sicil numarası gönderilmesinde 8.00 TL ücret alınır. Sicil ve şifrenin yatırımcıya gönderilmesinden sonra tekrar talep edilmesi halinde yeniden aynı ücret tahakkuk ettirilir. Tutar, BSMV hariç tutardır</t>
@@ -24050,9 +22354,6 @@
           <t>Ozel Bankacilik(YP)</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr"/>
-      <c r="D777" t="inlineStr"/>
-      <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -24080,9 +22381,6 @@
           <t>Özel Bankacılık</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr"/>
-      <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -24110,9 +22408,6 @@
           <t>Yatırım Merkezi</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr"/>
-      <c r="D779" t="inlineStr"/>
-      <c r="E779" t="inlineStr"/>
       <c r="F779" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -24140,9 +22435,6 @@
           <t>Yatırım Merkezi (YP)</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr"/>
       <c r="F780" t="inlineStr">
         <is>
           <t>0.05%</t>
@@ -24170,10 +22462,6 @@
           <t>Ozel Bankacilik</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
-      <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
           <t>20.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24196,10 +22484,6 @@
           <t>Ozel Bankacilik (YP)</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr"/>
-      <c r="E782" t="inlineStr"/>
-      <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
           <t>20.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24222,10 +22506,6 @@
           <t>Yatırım Merkezi</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr"/>
-      <c r="D783" t="inlineStr"/>
-      <c r="E783" t="inlineStr"/>
-      <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
           <t>20.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24248,10 +22528,6 @@
           <t>Yatırım Merkezi (YP)</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr"/>
-      <c r="E784" t="inlineStr"/>
-      <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr">
         <is>
           <t>20.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24274,10 +22550,6 @@
           <t>Şube</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr"/>
-      <c r="D785" t="inlineStr"/>
-      <c r="E785" t="inlineStr"/>
-      <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
           <t>5.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24300,10 +22572,6 @@
           <t>Şube (YP)</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr"/>
-      <c r="D786" t="inlineStr"/>
-      <c r="E786" t="inlineStr"/>
-      <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr">
         <is>
           <t>5.000TL üzerindeki, banka sistemi aracılığıyla gerçekleştirilen işlemler için geçerlidir. Tahsil edilen işlem ücretinin döviz cinsi, işlem yapılan kağıdın döviz cinsine bağlı olarak değişmektedir. (BSMV Dahil.)</t>
@@ -24331,13 +22599,11 @@
           <t>160.00TL</t>
         </is>
       </c>
-      <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr">
         <is>
           <t>180.00TL</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24365,13 +22631,11 @@
           <t>350.00TL</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr">
         <is>
           <t>360.00TL</t>
         </is>
       </c>
-      <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24399,13 +22663,11 @@
           <t>0TL</t>
         </is>
       </c>
-      <c r="D789" t="inlineStr"/>
       <c r="E789" t="inlineStr">
         <is>
           <t>300.00TL</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24433,13 +22695,11 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr">
         <is>
           <t>945.00TL</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
       <c r="G790" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24467,13 +22727,11 @@
           <t>980.00TL</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr"/>
       <c r="E791" t="inlineStr">
         <is>
           <t>1665.00TL</t>
         </is>
       </c>
-      <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24501,13 +22759,11 @@
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr">
         <is>
           <t>945.00TL</t>
         </is>
       </c>
-      <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24535,13 +22791,11 @@
           <t>1300.00TL</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr">
         <is>
           <t>1980.00TL</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24569,13 +22823,11 @@
           <t>1300.00TL</t>
         </is>
       </c>
-      <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr">
         <is>
           <t>1980.00TL</t>
         </is>
       </c>
-      <c r="F794" t="inlineStr"/>
       <c r="G794" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24603,13 +22855,11 @@
           <t>540.00TL</t>
         </is>
       </c>
-      <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr">
         <is>
           <t>900.00TL</t>
         </is>
       </c>
-      <c r="F795" t="inlineStr"/>
       <c r="G795" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24637,13 +22887,11 @@
           <t>980.00TL</t>
         </is>
       </c>
-      <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr">
         <is>
           <t>1665.00TL</t>
         </is>
       </c>
-      <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24671,13 +22919,11 @@
           <t>350.00TL</t>
         </is>
       </c>
-      <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr">
         <is>
           <t>405.00TL</t>
         </is>
       </c>
-      <c r="F797" t="inlineStr"/>
       <c r="G797" t="inlineStr">
         <is>
           <t>Asgari Tutar; yurt içi yerleşik ekran ücretlerini, Azami Tutar ise yurt dışı yerleşik (KKTC dahil) ekran ücretlerini göstermektedir. Ücretler aylık olarak tahsil edilmektedir</t>
@@ -24700,9 +22946,6 @@
           <t>Genel Saklama Ücreti</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr"/>
-      <c r="D798" t="inlineStr"/>
-      <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
           <t>1.00%</t>
@@ -24730,9 +22973,6 @@
           <t>Külçe Altın Kabulü (Şube)</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr"/>
-      <c r="D799" t="inlineStr"/>
-      <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
           <t>10.00%</t>
@@ -24760,9 +23000,6 @@
           <t>Külçe Altın Teslimatı (Şube)</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr"/>
-      <c r="D800" t="inlineStr"/>
-      <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
           <t>10.00%</t>
@@ -24790,13 +23027,11 @@
           <t>Yabancı/Yurt Dışı Kartlarla Yurt içi ATM'lerden Para Çekme</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
           <t>11.99%</t>
         </is>
       </c>
-      <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
           <t>11.99%</t>
@@ -24824,8 +23059,6 @@
           <t>Kredi Kartı Geçmiş Ekstre Ücreti</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr"/>
-      <c r="D802" t="inlineStr"/>
       <c r="E802" t="inlineStr">
         <is>
           <t>2.05TL</t>

--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
         <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -77,6 +83,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1304"/>
+  <dimension ref="A1:I1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -53853,6 +53862,805 @@
         </is>
       </c>
     </row>
+    <row r="1305">
+      <c r="A1305" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Eurobond Virman işlemleri</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Bankamızdan Diğer Bankaya Gönderilen İşlemler</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>50,00 EUR</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>500,00 EUR</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>İşlem başına nominal üzerinden</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Yurtiçi İhraçlı Yabancı Para Tahvil Bono Virman İşlemleri</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Bankamızdan Diğer Bankaya Gönderilen YP Kıymetler</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>20,00 EUR</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>500,00 EUR</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>İşlem başına nominal üzerinden</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>%0,03</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>%0,03</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>Nominal değer üzerinden yıllık olarak</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>ÖSBA, VDMK, VTMK,Kira Sertifikası Anapara ve Kupon İtfası</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>İşlem tutarı üzerinden alınır</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Hesap Açma</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>17,74 TL</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>17,74 TL</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>Açılan hesap başına 17,7492 TL hesap açma ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>MKK Hesap Bakım Ücreti</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>0,10 TL</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>0,10 TL</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>Saklama bakiyelerinin piyasa değeri 1000 TL ve üzeri olan hesaplardan günlük 0,1091 TL hesap bakım ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Yatırım Fonu Payı Alım Satım İşlem Ücretleri</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>%0,00001</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>İşlem tutarı üzerinden yüzbinde 1 minimum 1 kuruş alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>MKK DİBS Alım Satım İşlemleri Ücreti (İşlem Sayısı)</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>0,15 TL</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>0,15 TL</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>0,1554 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>MKK ÖSBA Alım-Satım Ücreti(İşlem Sayısı)</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>0,20 TL</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>0,20 TL</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>0,2083 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Üyelerarası menkul kıymet transferi</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>13,05 TL</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>13,05 TL</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>13,0507 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Üye İçi Hesaplararası</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>2,60 TL</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>2,60 TL</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>2,6099 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>%0,0001</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>%0,0001</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Diğer Yatırım Fonları</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, GS, KS VE DİBS (Anapara)</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>%0,65</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>%0,65</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>Yıllık nominal değerin yıllık onbinde 0,65'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, KS VE DİBS (KUPON)</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>%0,065</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>%0,065</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>Yıllık nominal değerin yıllık onbinde 0,065'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>MKK Yatırımcı Sicil Numarası ve Şifre Gönderim Ücreti</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>55,68 TL</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>55,68 TL</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>Yatırımcıya sicil numarası ve şifre gönderilme işlemleri için 55,6841 TL ücret alınır</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>TL Tahvil Bono  İşlemleri</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Bankamızdan Diğer Bankaya Gönderilen TL Kıymetler</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>250,00</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>1000,00</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>İşlem başına nominal üzerinden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/garanti_komisyonlar.xlsx
+++ b/garanti_komisyonlar.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1321"/>
+  <dimension ref="A1:I1398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -53870,37 +53870,37 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Eurobond Virman işlemleri</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>Bankamızdan Diğer Bankaya Gönderilen İşlemler</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
         <is>
-          <t>50,00 EUR</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>%0,05</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="F1305" t="inlineStr">
         <is>
-          <t>500,00 EUR</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1305" t="inlineStr">
         <is>
-          <t>%0,05</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="H1305" t="inlineStr">
         <is>
-          <t>İşlem başına nominal üzerinden</t>
+          <t>Dönem borcu 30.000 TL altında ise %3,25, 30.000 TL ve 180.000 TL arasında ise %3,75 , 180.000 TL üzerinde ise %4,25 olarak uygulanacaktır. Bireysel kredi kartları için geçerlidir. Faiz oranı üzerinden KKDF ve BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1305" t="inlineStr">
@@ -53917,37 +53917,37 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Yurtiçi İhraçlı Yabancı Para Tahvil Bono Virman İşlemleri</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>Bankamızdan Diğer Bankaya Gönderilen YP Kıymetler</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="D1306" t="inlineStr">
         <is>
-          <t>20,00 EUR</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>%0,05</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="F1306" t="inlineStr">
         <is>
-          <t>500,00 EUR</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1306" t="inlineStr">
         <is>
-          <t>%0,05</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="H1306" t="inlineStr">
         <is>
-          <t>İşlem başına nominal üzerinden</t>
+          <t>Paraf Esnaf, Paraf KOBİ, Paraf Business, HalkCard Business için geçerlidir. Faiz oranı üzerinden BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1306" t="inlineStr">
@@ -53964,37 +53964,37 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+          <t>Alışveriş Faiz Oranı</t>
         </is>
       </c>
       <c r="D1307" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>%0,03</t>
+          <t>%4,28</t>
         </is>
       </c>
       <c r="F1307" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1307" t="inlineStr">
         <is>
-          <t>%0,03</t>
+          <t>%4,28</t>
         </is>
       </c>
       <c r="H1307" t="inlineStr">
         <is>
-          <t>Nominal değer üzerinden yıllık olarak</t>
+          <t>K.K.T.C. için geçerlidir. Faiz oranı üzerinden FFF ve BSİV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1307" t="inlineStr">
@@ -54011,37 +54011,37 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>ÖSBA, VDMK, VTMK,Kira Sertifikası Anapara ve Kupon İtfası</t>
+          <t>Nakit Avans Komisyonu (Yurt içi / Yurt dışı)</t>
         </is>
       </c>
       <c r="D1308" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>%0,01</t>
+          <t>%1,00</t>
         </is>
       </c>
       <c r="F1308" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1308" t="inlineStr">
         <is>
-          <t>%0,01</t>
+          <t>%1,00</t>
         </is>
       </c>
       <c r="H1308" t="inlineStr">
         <is>
-          <t>İşlem tutarı üzerinden alınır</t>
+          <t>Bireysel ve Ticari Kredi kartları ile bankamız Şube, İnternet Şube, Dialog ve ATM’lerinden ve  yurt dışı diğer banka/kuruluş Şube ve ATM’lerinden kredi kart ile çekilen nakit avans tutarının %1’i üzerinden hesaplanmaktadır. Bireysel kredi kartı ile yurtiçi  diğer banka/kuruluş Şube ve ATM’lerinden kredi kartı ile çekilen nakit avans tutarının %3,88’i ile işlem başına 0,58 TL ücret alınmaktadır. Komisyon üzerinden BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1308" t="inlineStr">
@@ -54058,37 +54058,37 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
         <is>
-          <t>Hesap Açma</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="D1309" t="inlineStr">
         <is>
-          <t>17,74 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="F1309" t="inlineStr">
         <is>
-          <t>17,74 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1309" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="H1309" t="inlineStr">
         <is>
-          <t>Açılan hesap başına 17,7492 TL hesap açma ücreti alınır</t>
+          <t>Paraf Klasik,Paraf Gold,Paraf Platinum, Parafly, Parafly Platinum ve HalkCard için geçerlidir. Faiz oranı üzerinden KKDF ve BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1309" t="inlineStr">
@@ -54105,37 +54105,37 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr">
         <is>
-          <t>MKK Hesap Bakım Ücreti</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="D1310" t="inlineStr">
         <is>
-          <t>0,10 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="F1310" t="inlineStr">
         <is>
-          <t>0,10 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1310" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,25</t>
         </is>
       </c>
       <c r="H1310" t="inlineStr">
         <is>
-          <t>Saklama bakiyelerinin piyasa değeri 1000 TL ve üzeri olan hesaplardan günlük 0,1091 TL hesap bakım ücreti alınır</t>
+          <t>Paraf Business, Paraf Esnaf, Paraf Kobi, Paraf Kobi Eczacı, HalkCard Business, Paraf Kobi TOBB, Paraf Üreten Kadın ve Paraf Dijital Ticari kart için geçerlidir. Faiz oranı üzerinden BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1310" t="inlineStr">
@@ -54152,37 +54152,37 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr">
         <is>
-          <t>Yatırım Fonu Payı Alım Satım İşlem Ücretleri</t>
+          <t>Nakit Avans Faiz Oranı</t>
         </is>
       </c>
       <c r="D1311" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>%0,00001</t>
+          <t>%4,28</t>
         </is>
       </c>
       <c r="F1311" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1311" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,28</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
         <is>
-          <t>İşlem tutarı üzerinden yüzbinde 1 minimum 1 kuruş alınmaktadır</t>
+          <t>K.K.T.C için geçerlidir. Faiz oranı üzerinden FFF ve BSİV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1311" t="inlineStr">
@@ -54199,37 +54199,37 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>MKK DİBS Alım Satım İşlemleri Ücreti (İşlem Sayısı)</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="D1312" t="inlineStr">
         <is>
-          <t>0,15 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="F1312" t="inlineStr">
         <is>
-          <t>0,15 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1312" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="H1312" t="inlineStr">
         <is>
-          <t>0,1554 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+          <t>Dönem borcu 30.000TL altında ise %3,55, 30.000 TL ve 180.000 TL arasında ise %4,05, 180.000TL üzerinde ise %4,55 olarak uygulanacaktır. Faiz oranı üzerinden KKDF ve BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1312" t="inlineStr">
@@ -54246,37 +54246,37 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>MKK ÖSBA Alım-Satım Ücreti(İşlem Sayısı)</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr">
         <is>
-          <t>0,20 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="F1313" t="inlineStr">
         <is>
-          <t>0,20 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1313" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="H1313" t="inlineStr">
         <is>
-          <t>0,2083 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+          <t>Paraf Esnaf / Paraf KOBİ / Paraf Business / HalkCard Business için geçerlidir. Faiz oranı üzerinden BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1313" t="inlineStr">
@@ -54293,37 +54293,37 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Üyelerarası menkul kıymet transferi</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="D1314" t="inlineStr">
         <is>
-          <t>13,05 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,78</t>
         </is>
       </c>
       <c r="F1314" t="inlineStr">
         <is>
-          <t>13,05 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1314" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,78</t>
         </is>
       </c>
       <c r="H1314" t="inlineStr">
         <is>
-          <t>13,0507 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+          <t>K.K.T.C. için geçerlidir. Faiz oranı üzerinden FFF ve BSİV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1314" t="inlineStr">
@@ -54340,37 +54340,37 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Gecikme Faizi</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>Üye İçi Hesaplararası</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="D1315" t="inlineStr">
         <is>
-          <t>2,60 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="F1315" t="inlineStr">
         <is>
-          <t>2,60 TL</t>
+          <t>0,00 TL</t>
         </is>
       </c>
       <c r="G1315" t="inlineStr">
         <is>
-          <t>%0,00</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="H1315" t="inlineStr">
         <is>
-          <t>2,6099 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+          <t>Bireysel kartlarda Faiz oranı üzerinden KKDF ve BSMV tahsil edilmektedir</t>
         </is>
       </c>
       <c r="I1315" t="inlineStr">
@@ -54387,12 +54387,12 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Nakit Avans Gecikme Faizi</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi</t>
+          <t>Gecikme Faizi</t>
         </is>
       </c>
       <c r="D1316" t="inlineStr">
@@ -54402,7 +54402,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>%0,0001</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="F1316" t="inlineStr">
@@ -54412,12 +54412,12 @@
       </c>
       <c r="G1316" t="inlineStr">
         <is>
-          <t>%0,0001</t>
+          <t>%4,55</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
         <is>
-          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+          <t>Ticari kartlarda Faiz oranı üzerinden BSMV tahsil edilmektedir</t>
         </is>
       </c>
       <c r="I1316" t="inlineStr">
@@ -54434,37 +54434,37 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Kart Bedelleri</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>Diğer Yatırım Fonları</t>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>307,50</t>
         </is>
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>%0,01</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="F1317" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>307,50</t>
         </is>
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t>%0,01</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="H1317" t="inlineStr">
         <is>
-          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1317" t="inlineStr">
@@ -54481,37 +54481,37 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Kart Bedelleri</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, GS, KS VE DİBS (Anapara)</t>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
         </is>
       </c>
       <c r="D1318" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>147,00</t>
         </is>
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>%0,65</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="F1318" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>147,00</t>
         </is>
       </c>
       <c r="G1318" t="inlineStr">
         <is>
-          <t>%0,65</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="H1318" t="inlineStr">
         <is>
-          <t>Yıllık nominal değerin yıllık onbinde 0,65'i kadar saklama ücreti alınır</t>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1318" t="inlineStr">
@@ -54528,37 +54528,37 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Kart Bedelleri</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, KS VE DİBS (KUPON)</t>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>505,00</t>
         </is>
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>%0,065</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="F1319" t="inlineStr">
         <is>
-          <t>0,00 TL</t>
+          <t>505,00</t>
         </is>
       </c>
       <c r="G1319" t="inlineStr">
         <is>
-          <t>%0,065</t>
+          <t>%0,00</t>
         </is>
       </c>
       <c r="H1319" t="inlineStr">
         <is>
-          <t>Yıllık nominal değerin yıllık onbinde 0,065'i kadar saklama ücreti alınır</t>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1319" t="inlineStr">
@@ -54575,17 +54575,17 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+          <t>Kart Bedelleri</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>MKK Yatırımcı Sicil Numarası ve Şifre Gönderim Ücreti</t>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr">
         <is>
-          <t>55,68 TL</t>
+          <t>251,00</t>
         </is>
       </c>
       <c r="E1320" t="inlineStr">
@@ -54595,7 +54595,7 @@
       </c>
       <c r="F1320" t="inlineStr">
         <is>
-          <t>55,68 TL</t>
+          <t>251,00</t>
         </is>
       </c>
       <c r="G1320" t="inlineStr">
@@ -54605,7 +54605,7 @@
       </c>
       <c r="H1320" t="inlineStr">
         <is>
-          <t>Yatırımcıya sicil numarası ve şifre gönderilme işlemleri için 55,6841 TL ücret alınır</t>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
         </is>
       </c>
       <c r="I1320" t="inlineStr">
@@ -54622,40 +54622,3591 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>820,00</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>820,00</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>394,50</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>394,50</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>219,50</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. Öğrenci belgesi ibrazı halinde Gençİz kartlardan kampanya kapsamında kart ücreti alınmamaktadır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>Paraf Gencİz Kartın ek kartı bulunmamaktadır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>635,00</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>635,00</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>307,50</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>307,50</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>935,50</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>935,50</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. Parafly Platinum kartlardan kampanya kapsamında kart ücreti alınmamaktadır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>435,00</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>435,00</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>Yıllık Üyelik Bedeli bulunmamaktadır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Kart Üyelik Ücreti</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>Kart Üyelik Ücreti bulunmamaktadır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>4856,00</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>4856,00</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>2428,00</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>2428,00</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden oranında BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. Paraf RingPay kampanyalı ürün ve hizmet ücreti ayrıca tahsil edilmektedir</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>635,00</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>635,00</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>307,50</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>307,50</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>505,00</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir. Paraf Emekli / Paraf Değerlimiz kartlardan kampanya kapsamında kart ücreti alınmamaktadır</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>251,00</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Asıl Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>820,00</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>820,00</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Ek Kart Yıllık Üyelik Bedeli TL</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>394,50</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>394,50</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>Kredi kartının ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl, asıl ve ek kart sayısına göre, asıl kart hamilinden tahsil edilir. Kart aidatı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Kart Üyelik Ücreti (TL)</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>Kartın ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl kart hamilinden tahsil edilir. Kart üyelik ücreti üzerinden %5 oranında BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Kart Üyelik Ücreti (TL)</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>Kartın ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl kart hamilinden tahsil edilir. Kart üyelik ücreti üzerinden %5 oranında BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Paraf Üreten Kadın Kredi Kartı</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>Kartın ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl kart hamilinden tahsil edilir. Kart üyelik ücreti üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Kart Bedelleri</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Kart Üyelik Ücreti (TL)</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>1650,00 TL</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>Kartın ilk işlem tarihinden itibaren 1 yıl sonrasında ve her yıl kart hamilinden tahsil edilir. Kart üyelik ücreti üzerinden BSMV tahsil edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Fatura Ödemeleri ve Kurum Tahsilatları Ücreti</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>KREDİ KARTI FATURA KOMİSYONU</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>3,50 TL</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>%3,50</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>Bireysel kredi kartları ile yapılan anlık fatura ödemelerinde ve SGK (MOSİP) kurum tahsilatlarında 100 TL’ye kadar 3,50 TL, 100 TL üzeri ödemelerde %3,50 masraf alınır. BSMV hariçtir. Ticari kredi kartları ile yapılan SGK (MOSİP) kurum tahsilatlarında %3,50 masraf alınır. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Fatura Ödemeleri ve Kurum Tahsilatları Ücreti</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>SGK Prim Ödemeleri Komisyon Oranı</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>%3,50</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>%3,50</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>Sgk.gov.tr internet sitesi üzerinden kredi kartı ile gerçekleştirilen SGK Prim ödemelerinden %2,90 oranında Vade Farkı alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Anlık ve Otomatik Fatura Talimatı Faiz Oranı</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Otomatik Fatura Talimatı Faiz Oranı</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>Bireysel ve ticari kredi kartları ile gerçekleşen  otomatik fatura talimatlarında fatura tutarı üzerinden nakit avans faizi oranında alınır.  Faiz oranı üzerinden KKDF(Ticari kartlar hariç) , BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Anlık ve Otomatik Fatura Talimatı Faiz Oranı</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Anlık Fatura Faiz Oranı</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>Ticari Kredi kartları ile gerçekleşen anlık fatura ödemeleri üzerinden alınır. Faiz oranı üzerinden BSMV tahsil edilmektedir</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>PTT İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>PTT İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>59,49 TL</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>PTT şubeleri aracılığı ile yapılan kredi kartı ödemelerinden işlem tutarının %0,09’u oranında minimum 59,49 TL ücret tahsil edilir. BSMV hariçtir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Kira, Eğitim, Aidat Talimatı Komisyon Oranı</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Kira, Eğitim, Aidat Talimatı Komisyon Oranı</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>22,20 TL</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>%3,50</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>Kredi kartından verilen kira, eğitim, aidat talimatlarında talimat tutarının %3,50’si oranında minimum 22,20 TL ücret tahsis edilir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Borç Taksitlendirme Faizleri</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Aylık Faiz Oranı (%) (6-12 Ay)</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>6,7,8,9,12 ay için geçerli olup, faiz oranı üzerinden  KKDF ve BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Taksitli Nakit Avans Faizleri</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>3 Taksit</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>Bireysel Kartlarda Faiz oranı üzerinden KKDF ve BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Taksitli Nakit Avans Faizleri</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>3-6-9-12 Taksit</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>Ticari Kartlarda Faiz oranı üzerinden BSMV tahsil edilmektedir. BSİV müşteriden tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Diğer Ücret ve Komisyonlar</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Kampanyalı Ürün ve Hizmet Ücreti</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>750,00</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>Paraf RingPay ürününün Şubeden teslimi sonrasında kart ekstresine yansıtılacak tutardır. Ücret üzerinden BSMV tahsil edilmektedir</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Diğer Ücret ve Komisyonlar</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>3.Kişilere Ödenen Tutar</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>650,00</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>650,00</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>Paraf RingPay ürününün kayıp, çalıntı gibi nedenlerle yeniden talep edilmesi halinde banka tarafından ürün için 3.kişilere ödenen tutarlar müşterilerden tahsil edilmektedir</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Diğer Ücret ve Komisyonlar</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Ticari İşlem Faiz Oranı</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>%4,25</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>Paraf Esnaf ve Paraf Kobi ile KOBI/Esnaf POS'lardan yapılan vadeli/pesin/taksitli islemlerden kaynaklanan borcun vade tarihinde ödenmesi esastır. Borcun vade tarihinde ödenmeyen kısmına, vade tarihinden bir sonraki hesap kesim tarihine kadar isletilen faizdir.Vadeli işlem faiz oranı üzerinden BSMV tahsil edilir</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Eurobond Virman işlemleri</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Bankamızdan Diğer Bankaya Gönderilen İşlemler</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>50,00 EUR</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>500,00 EUR</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>İşlem başına nominal üzerinden</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Yurtiçi İhraçlı Yabancı Para Tahvil Bono Virman İşlemleri</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Bankamızdan Diğer Bankaya Gönderilen YP Kıymetler</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>20,00 EUR</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>500,00 EUR</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>%0,05</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>İşlem başına nominal üzerinden</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Eurobond ve Yurtdışında İhraç Edilen Diğer Borçlanma Araçları Saklama Ücreti</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>%0,03</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>%0,03</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>Nominal değer üzerinden yıllık olarak</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>ÖSBA, VDMK, VTMK,Kira Sertifikası Anapara ve Kupon İtfası</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>İşlem tutarı üzerinden alınır</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Hesap Açma</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>17,74 TL</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>17,74 TL</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>Açılan hesap başına 17,7492 TL hesap açma ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>MKK Hesap Bakım Ücreti</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>0,10 TL</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>0,10 TL</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>Saklama bakiyelerinin piyasa değeri 1000 TL ve üzeri olan hesaplardan günlük 0,1091 TL hesap bakım ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Yatırım Fonu Payı Alım Satım İşlem Ücretleri</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>%0,00001</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>İşlem tutarı üzerinden yüzbinde 1 minimum 1 kuruş alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>MKK DİBS Alım Satım İşlemleri Ücreti (İşlem Sayısı)</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>0,15 TL</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>0,15 TL</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>0,1554 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>MKK ÖSBA Alım-Satım Ücreti(İşlem Sayısı)</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>0,20 TL</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>0,20 TL</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>0,2083 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Üyelerarası menkul kıymet transferi</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>13,05 TL</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>13,05 TL</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>13,0507 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Üye İçi Hesaplararası</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>2,60 TL</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>2,60 TL</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>2,6099 TL olarak yapılan işlem sayısı başına alınmaktadır</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>%0,0001</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>%0,0001</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Diğer Yatırım Fonları</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>%0,01</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>Pay adedinin pay fiyatı ile çarpımının yıllık onbinde 1'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, GS, KS VE DİBS (Anapara)</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>%0,65</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>%0,65</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>Yıllık nominal değerin yıllık onbinde 0,65'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Özel Sektör Borçlanma Araçları, VDMK, VTMK, KS VE DİBS (KUPON)</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>%0,065</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>%0,065</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>Yıllık nominal değerin yıllık onbinde 0,065'i kadar saklama ücreti alınır</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Merkezi Kayıt Kuruluşu Masrafları</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>MKK Yatırımcı Sicil Numarası ve Şifre Gönderim Ücreti</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>55,68 TL</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>55,68 TL</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>Yatırımcıya sicil numarası ve şifre gönderilme işlemleri için 55,6841 TL ücret alınır</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
           <t>TL Tahvil Bono  İşlemleri</t>
         </is>
       </c>
-      <c r="C1321" t="inlineStr">
+      <c r="C1376" t="inlineStr">
         <is>
           <t>Bankamızdan Diğer Bankaya Gönderilen TL Kıymetler</t>
         </is>
       </c>
-      <c r="D1321" t="inlineStr">
+      <c r="D1376" t="inlineStr">
         <is>
           <t>250,00</t>
         </is>
       </c>
-      <c r="E1321" t="inlineStr">
+      <c r="E1376" t="inlineStr">
         <is>
           <t>%0,05</t>
         </is>
       </c>
-      <c r="F1321" t="inlineStr">
+      <c r="F1376" t="inlineStr">
         <is>
           <t>1000,00</t>
         </is>
       </c>
-      <c r="G1321" t="inlineStr">
+      <c r="G1376" t="inlineStr">
         <is>
           <t>%0,05</t>
         </is>
       </c>
-      <c r="H1321" t="inlineStr">
+      <c r="H1376" t="inlineStr">
         <is>
           <t>İşlem başına nominal üzerinden tahsil edilir</t>
         </is>
       </c>
-      <c r="I1321" t="inlineStr">
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Tahsil Amacı ile Alınan Senet</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Tahsil-Cüzdan</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>350,00 TL</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>%0,70</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>999999999999,00 TL</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>%0,70</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr"/>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Tahsil Amacı ile Alınan Senet</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Muamelesiz İade Masrafı</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr"/>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Senet Protestosu Kaldırma İşlemi (TL/YP)</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Protesto Kaldırma Masrafı</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>450,00 TL</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>450,00 TL</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr"/>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Diğer Banka Çekleri TL (Takas)</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Diğer Banka Çekleri Takas Masrafı</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr"/>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Diğer Banka Çekleri YP (Takas)</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Diğer Banka Çekleri (YP) Takas</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr"/>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Standart Çek (10 lu)</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>57,50 TL</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>Yaprak başı ücret bedelidir</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Standart Çek (25 lik)</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>50,00 TL</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>Yaprak başı ücret bedelidir</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Güvenceli Çek (10 luk)</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>95,00 TL</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>Yaprak başı ücret bedelidir</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Güvenceli Çek (25 lik)</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>80,00 TL</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>Yaprak başı ücret bedelidir</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Sürekli Form Çek</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>32,00 TL</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>Yaprak başı ücret bedelidir</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>ÇEK İŞLEMLERİ-Çek Karnesi İstihbarat Sabit Ücreti</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>800,00 TL</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>800,00 TL</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr"/>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>SAHTE/KAYIP/ÇALINTI/İPTAL ÇEK MASRAFI</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>150,00 TL</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>150,00 TL</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr"/>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Karşılıksız Çek İşlemleri TL / YP</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr"/>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Bedeli</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>3167 Karşılıksız Çek Yasa işlemleri TL Düzeltme Hakkı Kullanma Masrafı</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>800,00 TL</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>800,00 TL</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr"/>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Bloke Çek Düzenlenmesi (TL/YP)</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Bloke-Keşide Çek Düzenleme Komisyonu</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>2750,00 TL</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>%0,50</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr"/>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Çek Ödeme İşlemleri (Lehdardan Alınan)</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Otomatik Provizyon Şubeden Ödenen</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>400,00 TL</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr"/>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Çek Ödeme İşlemleri (Lehdardan Alınan)</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Tahsile Verilen Bankamız Çeklerinin Muamelesiz İadesi</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>100,00 TL</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>100,00 TL</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Çek İade</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Çek İade Ücreti</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>0,00 TL</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>100,00 TL</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr"/>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>KKTC Çek Masrafları</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>KKTC Diğer Banka Çekleri Takas Masrafı (TL/YP)</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>290,00</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr"/>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>KKTC Çek Masrafları</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>KKTC Aynı Şube Çeki Ödemesi  (TL/YP)</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>160,00</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr"/>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>KKTC Çek Masrafları</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>KKTC Farklı Şube Çeki Ödemesi (TL/YP)</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>290,00</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr"/>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="4" t="inlineStr">
+        <is>
+          <t>HALKBANK</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>KKTC Çek Masrafları</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>KKTC Otomatik Provizyonla Çek Ödeme</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>290,00</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>%0,00</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="inlineStr">
         <is>
           <t>31.07.2026</t>
         </is>
